--- a/www/bd/bd_indice_capacidad.xlsx
+++ b/www/bd/bd_indice_capacidad.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10921"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valeriacampuzano/Documents/MEXICO EVALUA/tuberia2024/shinytuberia/pestanaimpunidad/datos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valeriacampuzano/Documents/MEXICO EVALUA/DashboardsHallazgos/dashboardhallazgos/www/bd/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8947D24-C22B-0C43-BF63-C64CBFB4BF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B01B1ED-EFC8-1348-930B-6D7D961CBD37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16140" xr2:uid="{4072462F-AEDB-6444-BCF4-078F964151CC}"/>
   </bookViews>
   <sheets>
     <sheet name="general" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">general!$A$1:$D$705</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2020" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="55">
   <si>
     <t>Defensoría Pública</t>
   </si>
@@ -167,9 +170,6 @@
     <t>Presupuesto</t>
   </si>
   <si>
-    <t>Carrera judicial</t>
-  </si>
-  <si>
     <t>Autonomía constitucional</t>
   </si>
   <si>
@@ -188,9 +188,6 @@
     <t>Tasa de salas de audiencia por 100,000 hab</t>
   </si>
   <si>
-    <t>Tasa de fiscalías por cada 100,000 hab</t>
-  </si>
-  <si>
     <t>Ranking</t>
   </si>
   <si>
@@ -198,6 +195,15 @@
   </si>
   <si>
     <t>categoria</t>
+  </si>
+  <si>
+    <t>Comité de carrera judicial</t>
+  </si>
+  <si>
+    <t>Asuntos internos</t>
+  </si>
+  <si>
+    <t>Tasa de fiscalías por cada 100.000 hab</t>
   </si>
 </sst>
 </file>
@@ -207,7 +213,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -218,6 +224,19 @@
     <font>
       <b/>
       <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
@@ -240,18 +259,25 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -583,16 +609,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E624299-13BA-7F4D-9A79-35D067BBBF11}">
-  <dimension ref="A1:D673"/>
+  <dimension ref="A1:F705"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25.83203125" customWidth="1"/>
     <col min="2" max="2" width="68.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.5" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="2"/>
+    <col min="7" max="7" width="24.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
@@ -600,461 +627,493 @@
         <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="2">
-        <v>0.19342690594817474</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.23469999999999999</v>
+      </c>
+      <c r="E2" s="7"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="2">
-        <v>0.29504562998517436</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.3755</v>
+      </c>
+      <c r="E3" s="7"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="2">
-        <v>0.43626065035425282</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.52880000000000005</v>
+      </c>
+      <c r="E4" s="7"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="2">
-        <v>0.42008847048751763</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.27689999999999998</v>
+      </c>
+      <c r="E5" s="7"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="2">
-        <v>0.34685998320386602</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.39219999999999999</v>
+      </c>
+      <c r="E6" s="7"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="2">
-        <v>0.17957505204650631</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.1593</v>
+      </c>
+      <c r="E7" s="7"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2">
-        <v>0.25205173720458968</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.248</v>
+      </c>
+      <c r="E8" s="7"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
         <v>1</v>
       </c>
       <c r="D9" s="2">
-        <v>0.44483055312369502</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.50460000000000005</v>
+      </c>
+      <c r="E9" s="7"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
         <v>1</v>
       </c>
       <c r="D10" s="2">
-        <v>0.32313029076802746</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.3952</v>
+      </c>
+      <c r="E10" s="7"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
         <v>1</v>
       </c>
       <c r="D11" s="2">
-        <v>0.13492940561201058</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.17319999999999999</v>
+      </c>
+      <c r="E11" s="7"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
         <v>1</v>
       </c>
       <c r="D12" s="2">
-        <v>0.36983668373938039</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.41299999999999998</v>
+      </c>
+      <c r="E12" s="7"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C13" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="2">
-        <v>9.9868065845176587E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+        <v>9.7199999999999995E-2</v>
+      </c>
+      <c r="E13" s="7"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="2">
-        <v>0.14418054287420612</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.1188</v>
+      </c>
+      <c r="E14" s="7"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C15" t="s">
         <v>1</v>
       </c>
       <c r="D15" s="2">
-        <v>0.14242131660703453</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.14929999999999999</v>
+      </c>
+      <c r="E15" s="7"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16" t="s">
         <v>1</v>
       </c>
       <c r="D16" s="2">
-        <v>0.21239462497655301</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.1948</v>
+      </c>
+      <c r="E16" s="7"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C17" t="s">
         <v>1</v>
       </c>
       <c r="D17" s="2">
-        <v>0.21013199457500531</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.24510000000000001</v>
+      </c>
+      <c r="E17" s="7"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
         <v>1</v>
       </c>
       <c r="D18" s="2">
-        <v>0.22423128307519463</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.25490000000000002</v>
+      </c>
+      <c r="E18" s="7"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
         <v>1</v>
       </c>
       <c r="D19" s="2">
-        <v>0.29845662388169647</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.41020000000000001</v>
+      </c>
+      <c r="E19" s="7"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
         <v>1</v>
       </c>
       <c r="D20" s="2">
-        <v>0.34671622040764777</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.37890000000000001</v>
+      </c>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
         <v>1</v>
       </c>
       <c r="D21" s="2">
-        <v>0.18850701891649618</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.24379999999999999</v>
+      </c>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>19</v>
       </c>
       <c r="B22" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="2">
-        <v>0.21560266602512815</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.25019999999999998</v>
+      </c>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>20</v>
       </c>
       <c r="B23" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>1</v>
       </c>
       <c r="D23" s="2">
-        <v>0.44643455540092736</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.45569999999999999</v>
+      </c>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>0.21783112819306202</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.2079</v>
+      </c>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
         <v>1</v>
       </c>
       <c r="D25" s="2">
-        <v>0.11841867064368858</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.1227</v>
+      </c>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
         <v>1</v>
       </c>
       <c r="D26" s="2">
-        <v>0.15170349714186571</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.1638</v>
+      </c>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27" t="s">
         <v>1</v>
       </c>
       <c r="D27" s="2">
-        <v>0.24489174825353116</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.28039999999999998</v>
+      </c>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28" t="s">
         <v>1</v>
       </c>
       <c r="D28" s="2">
-        <v>0.1421255669592047</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.1928</v>
+      </c>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>26</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C29" t="s">
         <v>1</v>
       </c>
       <c r="D29" s="2">
-        <v>0.17916502277616075</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.1095</v>
+      </c>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>27</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
         <v>1</v>
       </c>
       <c r="D30" s="2">
-        <v>0.15545815321217596</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.19450000000000001</v>
+      </c>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
         <v>1</v>
       </c>
       <c r="D31" s="2">
-        <v>0.37145167244491523</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.30680000000000002</v>
+      </c>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
         <v>1</v>
       </c>
       <c r="D32" s="2">
-        <v>0.19077717806997316</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.23169999999999999</v>
+      </c>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C33" t="s">
         <v>1</v>
       </c>
       <c r="D33" s="2">
-        <v>0.17630919697237202</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0.20130000000000001</v>
+      </c>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>2</v>
       </c>
@@ -1068,7 +1127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -1082,7 +1141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -1096,7 +1155,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1107,10 +1166,10 @@
         <v>1</v>
       </c>
       <c r="D37" s="2">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -1124,7 +1183,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>6</v>
       </c>
@@ -1138,7 +1197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -1152,7 +1211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>8</v>
       </c>
@@ -1166,7 +1225,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -1180,7 +1239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>10</v>
       </c>
@@ -1194,7 +1253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>11</v>
       </c>
@@ -1208,7 +1267,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -1222,7 +1281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>13</v>
       </c>
@@ -1236,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -1250,7 +1309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>35</v>
       </c>
@@ -1512,8 +1571,8 @@
       <c r="C66" t="s">
         <v>1</v>
       </c>
-      <c r="D66" s="2">
-        <v>7.4200741444645807E-2</v>
+      <c r="D66" s="6">
+        <v>8.4099999999999994E-2</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -1526,8 +1585,8 @@
       <c r="C67" t="s">
         <v>1</v>
       </c>
-      <c r="D67" s="2">
-        <v>0.17016922532672998</v>
+      <c r="D67" s="6">
+        <v>0.1767</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -1540,8 +1599,8 @@
       <c r="C68" t="s">
         <v>1</v>
       </c>
-      <c r="D68" s="2">
-        <v>0.12559343422865821</v>
+      <c r="D68" s="6">
+        <v>0.1226</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -1554,8 +1613,8 @@
       <c r="C69" t="s">
         <v>1</v>
       </c>
-      <c r="D69" s="2">
-        <v>0.12058018656955313</v>
+      <c r="D69" s="6">
+        <v>0.1173</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -1568,8 +1627,8 @@
       <c r="C70" t="s">
         <v>1</v>
       </c>
-      <c r="D70" s="2">
-        <v>8.5424523909816946E-2</v>
+      <c r="D70" s="6">
+        <v>9.4399999999999998E-2</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -1582,8 +1641,8 @@
       <c r="C71" t="s">
         <v>1</v>
       </c>
-      <c r="D71" s="2">
-        <v>2.8076154821729433E-2</v>
+      <c r="D71" s="6">
+        <v>-5.16E-2</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -1596,8 +1655,8 @@
       <c r="C72" t="s">
         <v>1</v>
       </c>
-      <c r="D72" s="2">
-        <v>0.12586059594128773</v>
+      <c r="D72" s="6">
+        <v>0.1103</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -1610,8 +1669,8 @@
       <c r="C73" t="s">
         <v>1</v>
       </c>
-      <c r="D73" s="2">
-        <v>0.20594036906351004</v>
+      <c r="D73" s="6">
+        <v>0.2059</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -1624,8 +1683,8 @@
       <c r="C74" t="s">
         <v>1</v>
       </c>
-      <c r="D74" s="2">
-        <v>9.2938576620121852E-2</v>
+      <c r="D74" s="6">
+        <v>0.1057</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -1638,8 +1697,8 @@
       <c r="C75" t="s">
         <v>1</v>
       </c>
-      <c r="D75" s="2">
-        <v>7.2409785776028718E-2</v>
+      <c r="D75" s="6">
+        <v>7.4800000000000005E-2</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -1652,8 +1711,8 @@
       <c r="C76" t="s">
         <v>1</v>
       </c>
-      <c r="D76" s="2">
-        <v>5.8982915434660499E-2</v>
+      <c r="D76" s="6">
+        <v>6.88E-2</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -1666,8 +1725,8 @@
       <c r="C77" t="s">
         <v>1</v>
       </c>
-      <c r="D77" s="2">
-        <v>1.9084909665413624E-2</v>
+      <c r="D77" s="6">
+        <v>2.4199999999999999E-2</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -1680,8 +1739,8 @@
       <c r="C78" t="s">
         <v>1</v>
       </c>
-      <c r="D78" s="2">
-        <v>0.10100248919149038</v>
+      <c r="D78" s="6">
+        <v>0.1111</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -1694,8 +1753,8 @@
       <c r="C79" t="s">
         <v>1</v>
       </c>
-      <c r="D79" s="2">
-        <v>6.4902541604554026E-2</v>
+      <c r="D79" s="6">
+        <v>1.8200000000000001E-2</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -1708,8 +1767,8 @@
       <c r="C80" t="s">
         <v>1</v>
       </c>
-      <c r="D80" s="2">
-        <v>2.9379880738988451E-2</v>
+      <c r="D80" s="6">
+        <v>3.7199999999999997E-2</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -1722,8 +1781,8 @@
       <c r="C81" t="s">
         <v>1</v>
       </c>
-      <c r="D81" s="2">
-        <v>8.3047627183076914E-2</v>
+      <c r="D81" s="6">
+        <v>8.2699999999999996E-2</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -1736,8 +1795,8 @@
       <c r="C82" t="s">
         <v>1</v>
       </c>
-      <c r="D82" s="2">
-        <v>6.1820157236512414E-2</v>
+      <c r="D82" s="6">
+        <v>6.6400000000000001E-2</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -1750,8 +1809,8 @@
       <c r="C83" t="s">
         <v>1</v>
       </c>
-      <c r="D83" s="2">
-        <v>0.1307702589943244</v>
+      <c r="D83" s="6">
+        <v>0.1275</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -1764,8 +1823,8 @@
       <c r="C84" t="s">
         <v>1</v>
       </c>
-      <c r="D84" s="2">
-        <v>8.0866846736077691E-2</v>
+      <c r="D84" s="6">
+        <v>8.7400000000000005E-2</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -1778,8 +1837,8 @@
       <c r="C85" t="s">
         <v>1</v>
       </c>
-      <c r="D85" s="2">
-        <v>7.398180038576932E-2</v>
+      <c r="D85" s="6">
+        <v>7.9000000000000001E-2</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -1792,8 +1851,8 @@
       <c r="C86" t="s">
         <v>1</v>
       </c>
-      <c r="D86" s="2">
-        <v>0.10866448082180485</v>
+      <c r="D86" s="6">
+        <v>0.1119</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
@@ -1806,8 +1865,8 @@
       <c r="C87" t="s">
         <v>1</v>
       </c>
-      <c r="D87" s="2">
-        <v>0.16829757282070196</v>
+      <c r="D87" s="6">
+        <v>0.16070000000000001</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
@@ -1820,8 +1879,8 @@
       <c r="C88" t="s">
         <v>1</v>
       </c>
-      <c r="D88" s="2">
-        <v>5.7383981994014933E-2</v>
+      <c r="D88" s="6">
+        <v>7.7999999999999996E-3</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
@@ -1834,8 +1893,8 @@
       <c r="C89" t="s">
         <v>1</v>
       </c>
-      <c r="D89" s="2">
-        <v>5.8654485496002655E-2</v>
+      <c r="D89" s="6">
+        <v>6.1100000000000002E-2</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -1848,8 +1907,8 @@
       <c r="C90" t="s">
         <v>1</v>
       </c>
-      <c r="D90" s="2">
-        <v>5.2009875335451053E-2</v>
+      <c r="D90" s="6">
+        <v>4.6399999999999997E-2</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -1862,8 +1921,8 @@
       <c r="C91" t="s">
         <v>1</v>
       </c>
-      <c r="D91" s="2">
-        <v>9.2694003150573079E-2</v>
+      <c r="D91" s="6">
+        <v>0.1033</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -1876,8 +1935,8 @@
       <c r="C92" t="s">
         <v>1</v>
       </c>
-      <c r="D92" s="2">
-        <v>3.2350097422894297E-2</v>
+      <c r="D92" s="6">
+        <v>4.6300000000000001E-2</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
@@ -1890,8 +1949,8 @@
       <c r="C93" t="s">
         <v>1</v>
       </c>
-      <c r="D93" s="2">
-        <v>8.4781764110208033E-2</v>
+      <c r="D93" s="6">
+        <v>2.47E-2</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
@@ -1904,8 +1963,8 @@
       <c r="C94" t="s">
         <v>1</v>
       </c>
-      <c r="D94" s="2">
-        <v>7.9637296194457141E-2</v>
+      <c r="D94" s="6">
+        <v>9.2499999999999999E-2</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
@@ -1918,8 +1977,8 @@
       <c r="C95" t="s">
         <v>1</v>
       </c>
-      <c r="D95" s="2">
-        <v>8.3066416842370955E-2</v>
+      <c r="D95" s="6">
+        <v>8.7300000000000003E-2</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
@@ -1932,8 +1991,8 @@
       <c r="C96" t="s">
         <v>1</v>
       </c>
-      <c r="D96" s="2">
-        <v>8.815432496784037E-2</v>
+      <c r="D96" s="6">
+        <v>8.7400000000000005E-2</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
@@ -1946,8 +2005,8 @@
       <c r="C97" t="s">
         <v>1</v>
       </c>
-      <c r="D97" s="2">
-        <v>5.3836718508616779E-2</v>
+      <c r="D97" s="6">
+        <v>7.2700000000000001E-2</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
@@ -1960,8 +2019,8 @@
       <c r="C98" t="s">
         <v>1</v>
       </c>
-      <c r="D98" s="2">
-        <v>0.11922616450352895</v>
+      <c r="D98" s="6">
+        <v>0.1348</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
@@ -1974,8 +2033,8 @@
       <c r="C99" t="s">
         <v>1</v>
       </c>
-      <c r="D99" s="2">
-        <v>0.12487640465844439</v>
+      <c r="D99" s="6">
+        <v>0.14249999999999999</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
@@ -1988,8 +2047,8 @@
       <c r="C100" t="s">
         <v>1</v>
       </c>
-      <c r="D100" s="2">
-        <v>0.16066721612559459</v>
+      <c r="D100" s="6">
+        <v>0.18110000000000001</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
@@ -2002,8 +2061,8 @@
       <c r="C101" t="s">
         <v>1</v>
       </c>
-      <c r="D101" s="2">
-        <v>0.14950828391796453</v>
+      <c r="D101" s="6">
+        <v>0.13100000000000001</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
@@ -2016,8 +2075,8 @@
       <c r="C102" t="s">
         <v>1</v>
       </c>
-      <c r="D102" s="2">
-        <v>0.11143545929404911</v>
+      <c r="D102" s="6">
+        <v>0.1225</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
@@ -2030,8 +2089,8 @@
       <c r="C103" t="s">
         <v>1</v>
       </c>
-      <c r="D103" s="2">
-        <v>0.15149889722477689</v>
+      <c r="D103" s="6">
+        <v>0.17469999999999999</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
@@ -2044,8 +2103,8 @@
       <c r="C104" t="s">
         <v>1</v>
       </c>
-      <c r="D104" s="2">
-        <v>0.12096490656652406</v>
+      <c r="D104" s="6">
+        <v>0.12520000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
@@ -2058,8 +2117,8 @@
       <c r="C105" t="s">
         <v>1</v>
       </c>
-      <c r="D105" s="2">
-        <v>8.3785444580083343E-2</v>
+      <c r="D105" s="6">
+        <v>0.1147</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
@@ -2072,8 +2131,8 @@
       <c r="C106" t="s">
         <v>1</v>
       </c>
-      <c r="D106" s="2">
-        <v>0.2301917141479056</v>
+      <c r="D106" s="6">
+        <v>0.23019999999999999</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
@@ -2086,8 +2145,8 @@
       <c r="C107" t="s">
         <v>1</v>
       </c>
-      <c r="D107" s="2">
-        <v>5.9852539565335372E-2</v>
+      <c r="D107" s="6">
+        <v>7.6200000000000004E-2</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
@@ -2100,8 +2159,8 @@
       <c r="C108" t="s">
         <v>1</v>
       </c>
-      <c r="D108" s="2">
-        <v>0.16085376830471987</v>
+      <c r="D108" s="6">
+        <v>0.16880000000000001</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
@@ -2114,8 +2173,8 @@
       <c r="C109" t="s">
         <v>1</v>
       </c>
-      <c r="D109" s="2">
-        <v>7.6590415253605271E-2</v>
+      <c r="D109" s="6">
+        <v>4.8300000000000003E-2</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
@@ -2128,8 +2187,8 @@
       <c r="C110" t="s">
         <v>1</v>
       </c>
-      <c r="D110" s="2">
-        <v>4.3178053682715732E-2</v>
+      <c r="D110" s="6">
+        <v>5.1799999999999999E-2</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
@@ -2142,8 +2201,8 @@
       <c r="C111" t="s">
         <v>1</v>
       </c>
-      <c r="D111" s="2">
-        <v>7.75187750024805E-2</v>
+      <c r="D111" s="6">
+        <v>8.8999999999999996E-2</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
@@ -2156,8 +2215,8 @@
       <c r="C112" t="s">
         <v>1</v>
       </c>
-      <c r="D112" s="2">
-        <v>0.18301474423756456</v>
+      <c r="D112" s="6">
+        <v>0.1918</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
@@ -2170,8 +2229,8 @@
       <c r="C113" t="s">
         <v>1</v>
       </c>
-      <c r="D113" s="2">
-        <v>0.12708436739192841</v>
+      <c r="D113" s="6">
+        <v>0.14330000000000001</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
@@ -2184,8 +2243,8 @@
       <c r="C114" t="s">
         <v>1</v>
       </c>
-      <c r="D114" s="2">
-        <v>0.16241112583868222</v>
+      <c r="D114" s="6">
+        <v>0.1762</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
@@ -2198,8 +2257,8 @@
       <c r="C115" t="s">
         <v>1</v>
       </c>
-      <c r="D115" s="2">
-        <v>0.16768636488737204</v>
+      <c r="D115" s="6">
+        <v>0.19020000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
@@ -2212,8 +2271,8 @@
       <c r="C116" t="s">
         <v>1</v>
       </c>
-      <c r="D116" s="2">
-        <v>0.11584937367157007</v>
+      <c r="D116" s="6">
+        <v>0.12839999999999999</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
@@ -2226,8 +2285,8 @@
       <c r="C117" t="s">
         <v>1</v>
       </c>
-      <c r="D117" s="2">
-        <v>0.11452521853072686</v>
+      <c r="D117" s="6">
+        <v>0.129</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
@@ -2240,8 +2299,8 @@
       <c r="C118" t="s">
         <v>1</v>
       </c>
-      <c r="D118" s="2">
-        <v>0.10297884619762623</v>
+      <c r="D118" s="6">
+        <v>0.1168</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
@@ -2254,8 +2313,8 @@
       <c r="C119" t="s">
         <v>1</v>
       </c>
-      <c r="D119" s="2">
-        <v>0.12813698258022546</v>
+      <c r="D119" s="6">
+        <v>0.1295</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
@@ -2268,8 +2327,8 @@
       <c r="C120" t="s">
         <v>1</v>
       </c>
-      <c r="D120" s="2">
-        <v>0.15717006133722269</v>
+      <c r="D120" s="6">
+        <v>0.17630000000000001</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
@@ -2282,8 +2341,8 @@
       <c r="C121" t="s">
         <v>1</v>
       </c>
-      <c r="D121" s="2">
-        <v>5.9764185147685916E-2</v>
+      <c r="D121" s="6">
+        <v>5.3199999999999997E-2</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
@@ -2296,8 +2355,8 @@
       <c r="C122" t="s">
         <v>1</v>
       </c>
-      <c r="D122" s="2">
-        <v>9.9693621806414653E-2</v>
+      <c r="D122" s="6">
+        <v>0.1033</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
@@ -2310,8 +2369,8 @@
       <c r="C123" t="s">
         <v>1</v>
       </c>
-      <c r="D123" s="2">
-        <v>0.15219774510295808</v>
+      <c r="D123" s="6">
+        <v>0.16209999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
@@ -2324,8 +2383,8 @@
       <c r="C124" t="s">
         <v>1</v>
       </c>
-      <c r="D124" s="2">
-        <v>0.1097754695363104</v>
+      <c r="D124" s="6">
+        <v>0.13039999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
@@ -2338,8 +2397,8 @@
       <c r="C125" t="s">
         <v>1</v>
       </c>
-      <c r="D125" s="2">
-        <v>9.4383258665952735E-2</v>
+      <c r="D125" s="6">
+        <v>8.48E-2</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
@@ -2352,8 +2411,8 @@
       <c r="C126" t="s">
         <v>1</v>
       </c>
-      <c r="D126" s="2">
-        <v>7.5820857017718818E-2</v>
+      <c r="D126" s="6">
+        <v>8.5500000000000007E-2</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
@@ -2366,8 +2425,8 @@
       <c r="C127" t="s">
         <v>1</v>
       </c>
-      <c r="D127" s="2">
-        <v>8.838525560254426E-2</v>
+      <c r="D127" s="6">
+        <v>9.5699999999999993E-2</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
@@ -2380,8 +2439,8 @@
       <c r="C128" t="s">
         <v>1</v>
       </c>
-      <c r="D128" s="2">
-        <v>0.10262285310213279</v>
+      <c r="D128" s="6">
+        <v>0.1212</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
@@ -2394,8 +2453,8 @@
       <c r="C129" t="s">
         <v>1</v>
       </c>
-      <c r="D129" s="2">
-        <v>0.12247247846375525</v>
+      <c r="D129" s="6">
+        <v>0.1426</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
@@ -2408,8 +2467,8 @@
       <c r="C130" t="s">
         <v>1</v>
       </c>
-      <c r="D130" s="2">
-        <v>0</v>
+      <c r="D130" s="6">
+        <v>1.5800000000000002E-2</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
@@ -2422,8 +2481,8 @@
       <c r="C131" t="s">
         <v>1</v>
       </c>
-      <c r="D131" s="2">
-        <v>0</v>
+      <c r="D131" s="6">
+        <v>5.6300000000000003E-2</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
@@ -2436,8 +2495,8 @@
       <c r="C132" t="s">
         <v>1</v>
       </c>
-      <c r="D132" s="2">
-        <v>0</v>
+      <c r="D132" s="6">
+        <v>7.51E-2</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
@@ -2450,8 +2509,8 @@
       <c r="C133" t="s">
         <v>1</v>
       </c>
-      <c r="D133" s="2">
-        <v>0</v>
+      <c r="D133" s="6">
+        <v>2.87E-2</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
@@ -2464,8 +2523,8 @@
       <c r="C134" t="s">
         <v>1</v>
       </c>
-      <c r="D134" s="2">
-        <v>0</v>
+      <c r="D134" s="6">
+        <v>2.5399999999999999E-2</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
@@ -2478,8 +2537,8 @@
       <c r="C135" t="s">
         <v>1</v>
       </c>
-      <c r="D135" s="2">
-        <v>0</v>
+      <c r="D135" s="6">
+        <v>3.6200000000000003E-2</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
@@ -2492,8 +2551,8 @@
       <c r="C136" t="s">
         <v>1</v>
       </c>
-      <c r="D136" s="2">
-        <v>5.2262346967778634E-3</v>
+      <c r="D136" s="6">
+        <v>1.26E-2</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
@@ -2506,8 +2565,8 @@
       <c r="C137" t="s">
         <v>1</v>
       </c>
-      <c r="D137" s="2">
-        <v>5.1047394801016568E-3</v>
+      <c r="D137" s="6">
+        <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
@@ -2520,8 +2579,8 @@
       <c r="C138" t="s">
         <v>1</v>
       </c>
-      <c r="D138" s="2">
-        <v>0</v>
+      <c r="D138" s="6">
+        <v>5.9299999999999999E-2</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
@@ -2534,8 +2593,8 @@
       <c r="C139" t="s">
         <v>1</v>
       </c>
-      <c r="D139" s="2">
-        <v>2.6670802706464953E-3</v>
+      <c r="D139" s="6">
+        <v>2.2200000000000001E-2</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
@@ -2548,8 +2607,8 @@
       <c r="C140" t="s">
         <v>1</v>
       </c>
-      <c r="D140" s="2">
-        <v>0</v>
+      <c r="D140" s="6">
+        <v>2.5499999999999998E-2</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
@@ -2562,8 +2621,8 @@
       <c r="C141" t="s">
         <v>1</v>
       </c>
-      <c r="D141" s="2">
-        <v>4.1927409261576969E-3</v>
+      <c r="D141" s="6">
+        <v>2.4799999999999999E-2</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
@@ -2576,8 +2635,8 @@
       <c r="C142" t="s">
         <v>1</v>
       </c>
-      <c r="D142" s="2">
-        <v>0</v>
+      <c r="D142" s="6">
+        <v>-4.41E-2</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
@@ -2590,8 +2649,8 @@
       <c r="C143" t="s">
         <v>1</v>
       </c>
-      <c r="D143" s="2">
-        <v>0</v>
+      <c r="D143" s="6">
+        <v>4.2099999999999999E-2</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
@@ -2604,8 +2663,8 @@
       <c r="C144" t="s">
         <v>1</v>
       </c>
-      <c r="D144" s="2">
-        <v>0</v>
+      <c r="D144" s="6">
+        <v>-3.4099999999999998E-2</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
@@ -2618,8 +2677,8 @@
       <c r="C145" t="s">
         <v>1</v>
       </c>
-      <c r="D145" s="2">
-        <v>0</v>
+      <c r="D145" s="6">
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
@@ -2632,8 +2691,8 @@
       <c r="C146" t="s">
         <v>1</v>
       </c>
-      <c r="D146" s="2">
-        <v>0</v>
+      <c r="D146" s="6">
+        <v>1.2200000000000001E-2</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
@@ -2646,8 +2705,8 @@
       <c r="C147" t="s">
         <v>1</v>
       </c>
-      <c r="D147" s="2">
-        <v>0</v>
+      <c r="D147" s="6">
+        <v>9.2399999999999996E-2</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
@@ -2660,8 +2719,8 @@
       <c r="C148" t="s">
         <v>1</v>
       </c>
-      <c r="D148" s="2">
-        <v>0</v>
+      <c r="D148" s="6">
+        <v>1.3100000000000001E-2</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
@@ -2674,8 +2733,8 @@
       <c r="C149" t="s">
         <v>1</v>
       </c>
-      <c r="D149" s="2">
-        <v>0</v>
+      <c r="D149" s="6">
+        <v>3.5799999999999998E-2</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
@@ -2688,8 +2747,8 @@
       <c r="C150" t="s">
         <v>1</v>
       </c>
-      <c r="D150" s="2">
-        <v>3.9593390056970532E-3</v>
+      <c r="D150" s="6">
+        <v>2.1499999999999998E-2</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
@@ -2702,8 +2761,8 @@
       <c r="C151" t="s">
         <v>1</v>
       </c>
-      <c r="D151" s="2">
-        <v>0</v>
+      <c r="D151" s="6">
+        <v>1.55E-2</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
@@ -2716,8 +2775,8 @@
       <c r="C152" t="s">
         <v>1</v>
       </c>
-      <c r="D152" s="2">
-        <v>3.2770848618244013E-3</v>
+      <c r="D152" s="6">
+        <v>2.3800000000000002E-2</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
@@ -2730,8 +2789,8 @@
       <c r="C153" t="s">
         <v>1</v>
       </c>
-      <c r="D153" s="2">
-        <v>0</v>
+      <c r="D153" s="6">
+        <v>8.3999999999999995E-3</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
@@ -2744,8 +2803,8 @@
       <c r="C154" t="s">
         <v>1</v>
       </c>
-      <c r="D154" s="2">
-        <v>0</v>
+      <c r="D154" s="6">
+        <v>1.41E-2</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
@@ -2758,8 +2817,8 @@
       <c r="C155" t="s">
         <v>1</v>
       </c>
-      <c r="D155" s="2">
-        <v>0</v>
+      <c r="D155" s="6">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
@@ -2772,8 +2831,8 @@
       <c r="C156" t="s">
         <v>1</v>
       </c>
-      <c r="D156" s="2">
-        <v>0</v>
+      <c r="D156" s="6">
+        <v>1.61E-2</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
@@ -2786,7 +2845,7 @@
       <c r="C157" t="s">
         <v>1</v>
       </c>
-      <c r="D157" s="2">
+      <c r="D157" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2800,8 +2859,8 @@
       <c r="C158" t="s">
         <v>1</v>
       </c>
-      <c r="D158" s="2">
-        <v>0</v>
+      <c r="D158" s="6">
+        <v>1.6500000000000001E-2</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
@@ -2814,8 +2873,8 @@
       <c r="C159" t="s">
         <v>1</v>
       </c>
-      <c r="D159" s="2">
-        <v>0.2</v>
+      <c r="D159" s="6">
+        <v>0.12379999999999999</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
@@ -2828,8 +2887,8 @@
       <c r="C160" t="s">
         <v>1</v>
       </c>
-      <c r="D160" s="2">
-        <v>0</v>
+      <c r="D160" s="6">
+        <v>2.3E-2</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
@@ -2842,8 +2901,8 @@
       <c r="C161" t="s">
         <v>1</v>
       </c>
-      <c r="D161" s="2">
-        <v>0</v>
+      <c r="D161" s="6">
+        <v>-1.4E-2</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
@@ -2856,7 +2915,7 @@
       <c r="C162" t="s">
         <v>39</v>
       </c>
-      <c r="D162" s="2">
+      <c r="D162" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2870,7 +2929,7 @@
       <c r="C163" t="s">
         <v>39</v>
       </c>
-      <c r="D163" s="2">
+      <c r="D163" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2884,7 +2943,7 @@
       <c r="C164" t="s">
         <v>39</v>
       </c>
-      <c r="D164" s="2">
+      <c r="D164" s="6">
         <v>0.15</v>
       </c>
     </row>
@@ -2898,8 +2957,8 @@
       <c r="C165" t="s">
         <v>39</v>
       </c>
-      <c r="D165" s="2">
-        <v>0.15</v>
+      <c r="D165" s="6">
+        <v>0</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
@@ -2912,7 +2971,7 @@
       <c r="C166" t="s">
         <v>39</v>
       </c>
-      <c r="D166" s="2">
+      <c r="D166" s="6">
         <v>0.15</v>
       </c>
     </row>
@@ -2926,7 +2985,7 @@
       <c r="C167" t="s">
         <v>39</v>
       </c>
-      <c r="D167" s="2">
+      <c r="D167" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2940,7 +2999,7 @@
       <c r="C168" t="s">
         <v>39</v>
       </c>
-      <c r="D168" s="2">
+      <c r="D168" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2954,7 +3013,7 @@
       <c r="C169" t="s">
         <v>39</v>
       </c>
-      <c r="D169" s="2">
+      <c r="D169" s="6">
         <v>0.15</v>
       </c>
     </row>
@@ -2968,7 +3027,7 @@
       <c r="C170" t="s">
         <v>39</v>
       </c>
-      <c r="D170" s="2">
+      <c r="D170" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2982,7 +3041,7 @@
       <c r="C171" t="s">
         <v>39</v>
       </c>
-      <c r="D171" s="2">
+      <c r="D171" s="6">
         <v>0</v>
       </c>
     </row>
@@ -2996,7 +3055,7 @@
       <c r="C172" t="s">
         <v>39</v>
       </c>
-      <c r="D172" s="2">
+      <c r="D172" s="6">
         <v>0.15</v>
       </c>
     </row>
@@ -3010,7 +3069,7 @@
       <c r="C173" t="s">
         <v>39</v>
       </c>
-      <c r="D173" s="2">
+      <c r="D173" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3024,7 +3083,7 @@
       <c r="C174" t="s">
         <v>39</v>
       </c>
-      <c r="D174" s="2">
+      <c r="D174" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3038,7 +3097,7 @@
       <c r="C175" t="s">
         <v>39</v>
       </c>
-      <c r="D175" s="2">
+      <c r="D175" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3052,7 +3111,7 @@
       <c r="C176" t="s">
         <v>39</v>
       </c>
-      <c r="D176" s="2">
+      <c r="D176" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3066,7 +3125,7 @@
       <c r="C177" t="s">
         <v>39</v>
       </c>
-      <c r="D177" s="2">
+      <c r="D177" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3080,7 +3139,7 @@
       <c r="C178" t="s">
         <v>39</v>
       </c>
-      <c r="D178" s="2">
+      <c r="D178" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3094,7 +3153,7 @@
       <c r="C179" t="s">
         <v>39</v>
       </c>
-      <c r="D179" s="2">
+      <c r="D179" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3108,7 +3167,7 @@
       <c r="C180" t="s">
         <v>39</v>
       </c>
-      <c r="D180" s="2">
+      <c r="D180" s="6">
         <v>0.15</v>
       </c>
     </row>
@@ -3122,7 +3181,7 @@
       <c r="C181" t="s">
         <v>39</v>
       </c>
-      <c r="D181" s="2">
+      <c r="D181" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3136,7 +3195,7 @@
       <c r="C182" t="s">
         <v>39</v>
       </c>
-      <c r="D182" s="2">
+      <c r="D182" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3150,7 +3209,7 @@
       <c r="C183" t="s">
         <v>39</v>
       </c>
-      <c r="D183" s="2">
+      <c r="D183" s="6">
         <v>0.15</v>
       </c>
     </row>
@@ -3164,7 +3223,7 @@
       <c r="C184" t="s">
         <v>39</v>
       </c>
-      <c r="D184" s="2">
+      <c r="D184" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3178,7 +3237,7 @@
       <c r="C185" t="s">
         <v>39</v>
       </c>
-      <c r="D185" s="2">
+      <c r="D185" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3192,7 +3251,7 @@
       <c r="C186" t="s">
         <v>39</v>
       </c>
-      <c r="D186" s="2">
+      <c r="D186" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3206,7 +3265,7 @@
       <c r="C187" t="s">
         <v>39</v>
       </c>
-      <c r="D187" s="2">
+      <c r="D187" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3220,7 +3279,7 @@
       <c r="C188" t="s">
         <v>39</v>
       </c>
-      <c r="D188" s="2">
+      <c r="D188" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3234,7 +3293,7 @@
       <c r="C189" t="s">
         <v>39</v>
       </c>
-      <c r="D189" s="2">
+      <c r="D189" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3248,7 +3307,7 @@
       <c r="C190" t="s">
         <v>39</v>
       </c>
-      <c r="D190" s="2">
+      <c r="D190" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3262,7 +3321,7 @@
       <c r="C191" t="s">
         <v>39</v>
       </c>
-      <c r="D191" s="2">
+      <c r="D191" s="6">
         <v>0</v>
       </c>
     </row>
@@ -3276,11 +3335,11 @@
       <c r="C192" t="s">
         <v>39</v>
       </c>
-      <c r="D192" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D192" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
         <v>29</v>
       </c>
@@ -3290,11 +3349,11 @@
       <c r="C193" t="s">
         <v>39</v>
       </c>
-      <c r="D193" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D193" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
         <v>2</v>
       </c>
@@ -3304,11 +3363,13 @@
       <c r="C194" t="s">
         <v>31</v>
       </c>
-      <c r="D194" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D194" s="5">
+        <v>9.9000000000000008E-3</v>
+      </c>
+      <c r="E194" s="4"/>
+      <c r="F194" s="4"/>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>3</v>
       </c>
@@ -3318,11 +3379,13 @@
       <c r="C195" t="s">
         <v>31</v>
       </c>
-      <c r="D195" s="2">
-        <v>1.2370129870129866E-2</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D195" s="5">
+        <v>1.89E-2</v>
+      </c>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
         <v>4</v>
       </c>
@@ -3332,11 +3395,13 @@
       <c r="C196" t="s">
         <v>31</v>
       </c>
-      <c r="D196" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D196" s="5">
+        <v>-3.0000000000000001E-3</v>
+      </c>
+      <c r="E196" s="4"/>
+      <c r="F196" s="4"/>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
         <v>5</v>
       </c>
@@ -3346,11 +3411,13 @@
       <c r="C197" t="s">
         <v>31</v>
       </c>
-      <c r="D197" s="2">
-        <v>2.5198412698412685E-2</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D197" s="5">
+        <v>2.1899999999999999E-2</v>
+      </c>
+      <c r="E197" s="4"/>
+      <c r="F197" s="4"/>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
         <v>33</v>
       </c>
@@ -3360,11 +3427,13 @@
       <c r="C198" t="s">
         <v>31</v>
       </c>
-      <c r="D198" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D198" s="5">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="E198" s="4"/>
+      <c r="F198" s="4"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>6</v>
       </c>
@@ -3374,11 +3443,13 @@
       <c r="C199" t="s">
         <v>31</v>
       </c>
-      <c r="D199" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D199" s="5">
+        <v>-4.8899999999999999E-2</v>
+      </c>
+      <c r="E199" s="4"/>
+      <c r="F199" s="4"/>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
         <v>7</v>
       </c>
@@ -3388,11 +3459,13 @@
       <c r="C200" t="s">
         <v>31</v>
       </c>
-      <c r="D200" s="2">
-        <v>4.0821428571428564E-2</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D200" s="5">
+        <v>2.52E-2</v>
+      </c>
+      <c r="E200" s="4"/>
+      <c r="F200" s="4"/>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
         <v>8</v>
       </c>
@@ -3402,11 +3475,13 @@
       <c r="C201" t="s">
         <v>31</v>
       </c>
-      <c r="D201" s="2">
+      <c r="D201" s="5">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E201" s="4"/>
+      <c r="F201" s="4"/>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -3416,11 +3491,13 @@
       <c r="C202" t="s">
         <v>31</v>
       </c>
-      <c r="D202" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D202" s="5">
+        <v>1.2699999999999999E-2</v>
+      </c>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4"/>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
         <v>10</v>
       </c>
@@ -3430,11 +3507,13 @@
       <c r="C203" t="s">
         <v>31</v>
       </c>
-      <c r="D203" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D203" s="5">
+        <v>5.7000000000000002E-3</v>
+      </c>
+      <c r="E203" s="4"/>
+      <c r="F203" s="4"/>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
         <v>11</v>
       </c>
@@ -3444,11 +3523,13 @@
       <c r="C204" t="s">
         <v>31</v>
       </c>
-      <c r="D204" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D204" s="5">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="E204" s="4"/>
+      <c r="F204" s="4"/>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
         <v>12</v>
       </c>
@@ -3458,11 +3539,13 @@
       <c r="C205" t="s">
         <v>31</v>
       </c>
-      <c r="D205" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D205" s="5">
+        <v>5.1000000000000004E-3</v>
+      </c>
+      <c r="E205" s="4"/>
+      <c r="F205" s="4"/>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
         <v>13</v>
       </c>
@@ -3472,11 +3555,13 @@
       <c r="C206" t="s">
         <v>31</v>
       </c>
-      <c r="D206" s="2">
-        <v>6.8035714285714184E-3</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D206" s="5">
+        <v>1.6899999999999998E-2</v>
+      </c>
+      <c r="E206" s="4"/>
+      <c r="F206" s="4"/>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
         <v>14</v>
       </c>
@@ -3486,11 +3571,13 @@
       <c r="C207" t="s">
         <v>31</v>
       </c>
-      <c r="D207" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D207" s="5">
+        <v>-4.6699999999999998E-2</v>
+      </c>
+      <c r="E207" s="4"/>
+      <c r="F207" s="4"/>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
         <v>35</v>
       </c>
@@ -3500,11 +3587,13 @@
       <c r="C208" t="s">
         <v>31</v>
       </c>
-      <c r="D208" s="2">
-        <v>3.4017857142857287E-3</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D208" s="5">
+        <v>1.12E-2</v>
+      </c>
+      <c r="E208" s="4"/>
+      <c r="F208" s="4"/>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
         <v>34</v>
       </c>
@@ -3514,11 +3603,13 @@
       <c r="C209" t="s">
         <v>31</v>
       </c>
-      <c r="D209" s="2">
-        <v>1.4920112781954873E-2</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D209" s="5">
+        <v>1.4500000000000001E-2</v>
+      </c>
+      <c r="E209" s="4"/>
+      <c r="F209" s="4"/>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
         <v>15</v>
       </c>
@@ -3528,11 +3619,13 @@
       <c r="C210" t="s">
         <v>31</v>
       </c>
-      <c r="D210" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D210" s="5">
+        <v>4.5999999999999999E-3</v>
+      </c>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4"/>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
         <v>16</v>
       </c>
@@ -3542,11 +3635,13 @@
       <c r="C211" t="s">
         <v>31</v>
       </c>
-      <c r="D211" s="2">
-        <v>4.3197278911564614E-2</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D211" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="E211" s="4"/>
+      <c r="F211" s="4"/>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>17</v>
       </c>
@@ -3556,11 +3651,13 @@
       <c r="C212" t="s">
         <v>31</v>
       </c>
-      <c r="D212" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D212" s="5">
+        <v>6.4999999999999997E-3</v>
+      </c>
+      <c r="E212" s="4"/>
+      <c r="F212" s="4"/>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -3570,11 +3667,13 @@
       <c r="C213" t="s">
         <v>31</v>
       </c>
-      <c r="D213" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D213" s="5">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E213" s="4"/>
+      <c r="F213" s="4"/>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>19</v>
       </c>
@@ -3584,11 +3683,13 @@
       <c r="C214" t="s">
         <v>31</v>
       </c>
-      <c r="D214" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D214" s="5">
+        <v>3.2000000000000002E-3</v>
+      </c>
+      <c r="E214" s="4"/>
+      <c r="F214" s="4"/>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>20</v>
       </c>
@@ -3598,11 +3699,13 @@
       <c r="C215" t="s">
         <v>31</v>
       </c>
-      <c r="D215" s="2">
-        <v>2.8348214285714293E-2</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D215" s="5">
+        <v>2.0799999999999999E-2</v>
+      </c>
+      <c r="E215" s="4"/>
+      <c r="F215" s="4"/>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
         <v>21</v>
       </c>
@@ -3612,11 +3715,13 @@
       <c r="C216" t="s">
         <v>31</v>
       </c>
-      <c r="D216" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D216" s="5">
+        <v>-4.9599999999999998E-2</v>
+      </c>
+      <c r="E216" s="4"/>
+      <c r="F216" s="4"/>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
         <v>22</v>
       </c>
@@ -3626,11 +3731,13 @@
       <c r="C217" t="s">
         <v>31</v>
       </c>
-      <c r="D217" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D217" s="5">
+        <v>2.3999999999999998E-3</v>
+      </c>
+      <c r="E217" s="4"/>
+      <c r="F217" s="4"/>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
         <v>23</v>
       </c>
@@ -3640,11 +3747,13 @@
       <c r="C218" t="s">
         <v>31</v>
       </c>
-      <c r="D218" s="2">
-        <v>2.7214285714285736E-2</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D218" s="5">
+        <v>2.1600000000000001E-2</v>
+      </c>
+      <c r="E218" s="4"/>
+      <c r="F218" s="4"/>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
         <v>24</v>
       </c>
@@ -3654,11 +3763,13 @@
       <c r="C219" t="s">
         <v>31</v>
       </c>
-      <c r="D219" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D219" s="5">
+        <v>1.06E-2</v>
+      </c>
+      <c r="E219" s="4"/>
+      <c r="F219" s="4"/>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
         <v>25</v>
       </c>
@@ -3668,11 +3779,13 @@
       <c r="C220" t="s">
         <v>31</v>
       </c>
-      <c r="D220" s="2">
-        <v>4.7247023809523806E-3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D220" s="5">
+        <v>1.8700000000000001E-2</v>
+      </c>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4"/>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
         <v>26</v>
       </c>
@@ -3682,11 +3795,13 @@
       <c r="C221" t="s">
         <v>31</v>
       </c>
-      <c r="D221" s="2">
-        <v>1.828917050691245E-2</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D221" s="5">
+        <v>1.7100000000000001E-2</v>
+      </c>
+      <c r="E221" s="4"/>
+      <c r="F221" s="4"/>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A222" t="s">
         <v>27</v>
       </c>
@@ -3696,11 +3811,13 @@
       <c r="C222" t="s">
         <v>31</v>
       </c>
-      <c r="D222" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D222" s="5">
+        <v>1.2800000000000001E-2</v>
+      </c>
+      <c r="E222" s="4"/>
+      <c r="F222" s="4"/>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
         <v>36</v>
       </c>
@@ -3710,11 +3827,13 @@
       <c r="C223" t="s">
         <v>31</v>
       </c>
-      <c r="D223" s="2">
-        <v>5.0772921108742063E-3</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D223" s="5">
+        <v>9.2999999999999992E-3</v>
+      </c>
+      <c r="E223" s="4"/>
+      <c r="F223" s="4"/>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A224" t="s">
         <v>28</v>
       </c>
@@ -3724,11 +3843,13 @@
       <c r="C224" t="s">
         <v>31</v>
       </c>
-      <c r="D224" s="2">
-        <v>1.7008928571428591E-2</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D224" s="5">
+        <v>1.6299999999999999E-2</v>
+      </c>
+      <c r="E224" s="4"/>
+      <c r="F224" s="4"/>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A225" t="s">
         <v>29</v>
       </c>
@@ -3738,11 +3859,13 @@
       <c r="C225" t="s">
         <v>31</v>
       </c>
-      <c r="D225" s="2">
-        <v>2.7656794425087025E-3</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D225" s="5">
+        <v>2.1700000000000001E-2</v>
+      </c>
+      <c r="E225" s="4"/>
+      <c r="F225" s="4"/>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>2</v>
       </c>
@@ -3752,11 +3875,11 @@
       <c r="C226" t="s">
         <v>31</v>
       </c>
-      <c r="D226" s="2">
-        <v>3.0988312736272082E-2</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D226" s="6">
+        <v>3.1E-2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>3</v>
       </c>
@@ -3766,11 +3889,11 @@
       <c r="C227" t="s">
         <v>31</v>
       </c>
-      <c r="D227" s="2">
-        <v>9.5389142073492569E-2</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D227" s="6">
+        <v>9.5399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>4</v>
       </c>
@@ -3780,11 +3903,11 @@
       <c r="C228" t="s">
         <v>31</v>
       </c>
-      <c r="D228" s="2">
-        <v>2.8443338174815629E-2</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D228" s="6">
+        <v>2.8400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>5</v>
       </c>
@@ -3794,11 +3917,11 @@
       <c r="C229" t="s">
         <v>31</v>
       </c>
-      <c r="D229" s="2">
-        <v>2.3722181446338645E-3</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D229" s="6">
+        <v>2.3999999999999998E-3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>33</v>
       </c>
@@ -3808,11 +3931,11 @@
       <c r="C230" t="s">
         <v>31</v>
       </c>
-      <c r="D230" s="2">
-        <v>5.8959489903722996E-2</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D230" s="6">
+        <v>5.8999999999999997E-2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>6</v>
       </c>
@@ -3822,11 +3945,11 @@
       <c r="C231" t="s">
         <v>31</v>
       </c>
-      <c r="D231" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D231" s="6">
+        <v>-3.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>7</v>
       </c>
@@ -3836,11 +3959,11 @@
       <c r="C232" t="s">
         <v>31</v>
       </c>
-      <c r="D232" s="2">
-        <v>2.6602151917720307E-2</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D232" s="6">
+        <v>2.6599999999999999E-2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>8</v>
       </c>
@@ -3850,11 +3973,11 @@
       <c r="C233" t="s">
         <v>31</v>
       </c>
-      <c r="D233" s="2">
-        <v>5.9403690635100566E-3</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D233" s="6">
+        <v>5.8999999999999999E-3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>9</v>
       </c>
@@ -3864,11 +3987,11 @@
       <c r="C234" t="s">
         <v>31</v>
       </c>
-      <c r="D234" s="2">
-        <v>1.7297982069381435E-2</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D234" s="6">
+        <v>1.7299999999999999E-2</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>10</v>
       </c>
@@ -3878,11 +4001,11 @@
       <c r="C235" t="s">
         <v>31</v>
       </c>
-      <c r="D235" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D235" s="6">
+        <v>-3.3E-3</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>11</v>
       </c>
@@ -3892,11 +4015,11 @@
       <c r="C236" t="s">
         <v>31</v>
       </c>
-      <c r="D236" s="2">
-        <v>2.9939673855714687E-2</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D236" s="6">
+        <v>2.9899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>12</v>
       </c>
@@ -3906,11 +4029,11 @@
       <c r="C237" t="s">
         <v>31</v>
       </c>
-      <c r="D237" s="2">
-        <v>9.0966657790249594E-3</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D237" s="6">
+        <v>9.1000000000000004E-3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>13</v>
       </c>
@@ -3920,11 +4043,11 @@
       <c r="C238" t="s">
         <v>31</v>
       </c>
-      <c r="D238" s="2">
-        <v>2.4956175949561045E-2</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D238" s="6">
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>14</v>
       </c>
@@ -3934,11 +4057,11 @@
       <c r="C239" t="s">
         <v>31</v>
       </c>
-      <c r="D239" s="2">
-        <v>1.0802901865722535E-2</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D239" s="6">
+        <v>1.0800000000000001E-2</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>35</v>
       </c>
@@ -3948,8 +4071,8 @@
       <c r="C240" t="s">
         <v>31</v>
       </c>
-      <c r="D240" s="2">
-        <v>7.1127013424776998E-3</v>
+      <c r="D240" s="6">
+        <v>7.1000000000000004E-3</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
@@ -3962,8 +4085,8 @@
       <c r="C241" t="s">
         <v>31</v>
       </c>
-      <c r="D241" s="2">
-        <v>1.0440164879914112E-2</v>
+      <c r="D241" s="6">
+        <v>1.04E-2</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
@@ -3976,8 +4099,8 @@
       <c r="C242" t="s">
         <v>31</v>
       </c>
-      <c r="D242" s="2">
-        <v>4.6775340695307116E-2</v>
+      <c r="D242" s="6">
+        <v>4.6800000000000001E-2</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
@@ -3990,8 +4113,8 @@
       <c r="C243" t="s">
         <v>31</v>
       </c>
-      <c r="D243" s="2">
-        <v>1.8181688033705741E-2</v>
+      <c r="D243" s="6">
+        <v>1.8200000000000001E-2</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
@@ -4004,8 +4127,8 @@
       <c r="C244" t="s">
         <v>31</v>
       </c>
-      <c r="D244" s="2">
-        <v>1.7455815399463153E-2</v>
+      <c r="D244" s="6">
+        <v>1.7500000000000002E-2</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
@@ -4018,8 +4141,8 @@
       <c r="C245" t="s">
         <v>31</v>
       </c>
-      <c r="D245" s="2">
-        <v>6.864685846368482E-3</v>
+      <c r="D245" s="6">
+        <v>6.8999999999999999E-3</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
@@ -4032,7 +4155,7 @@
       <c r="C246" t="s">
         <v>31</v>
       </c>
-      <c r="D246" s="2">
+      <c r="D246" s="6">
         <v>0.1</v>
       </c>
     </row>
@@ -4046,8 +4169,8 @@
       <c r="C247" t="s">
         <v>31</v>
       </c>
-      <c r="D247" s="2">
-        <v>6.682931568170522E-2</v>
+      <c r="D247" s="6">
+        <v>6.6799999999999998E-2</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
@@ -4060,8 +4183,8 @@
       <c r="C248" t="s">
         <v>31</v>
       </c>
-      <c r="D248" s="2">
-        <v>2.5455676106381747E-2</v>
+      <c r="D248" s="6">
+        <v>2.5499999999999998E-2</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
@@ -4074,8 +4197,8 @@
       <c r="C249" t="s">
         <v>31</v>
       </c>
-      <c r="D249" s="2">
-        <v>-1.0468098399229397E-3</v>
+      <c r="D249" s="6">
+        <v>-1E-3</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
@@ -4088,8 +4211,8 @@
       <c r="C250" t="s">
         <v>31</v>
       </c>
-      <c r="D250" s="2">
-        <v>1.3488996934958192E-2</v>
+      <c r="D250" s="6">
+        <v>1.35E-2</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
@@ -4102,8 +4225,8 @@
       <c r="C251" t="s">
         <v>31</v>
       </c>
-      <c r="D251" s="2">
-        <v>2.7198238090166475E-2</v>
+      <c r="D251" s="6">
+        <v>2.7199999999999998E-2</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
@@ -4116,8 +4239,8 @@
       <c r="C252" t="s">
         <v>31</v>
       </c>
-      <c r="D252" s="2">
-        <v>5.3086176130615311E-3</v>
+      <c r="D252" s="6">
+        <v>5.3E-3</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
@@ -4130,8 +4253,8 @@
       <c r="C253" t="s">
         <v>31</v>
       </c>
-      <c r="D253" s="2">
-        <v>0</v>
+      <c r="D253" s="6">
+        <v>-5.8900000000000001E-2</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
@@ -4144,8 +4267,8 @@
       <c r="C254" t="s">
         <v>31</v>
       </c>
-      <c r="D254" s="2">
-        <v>2.1992099384973603E-2</v>
+      <c r="D254" s="6">
+        <v>2.1999999999999999E-2</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
@@ -4158,8 +4281,8 @@
       <c r="C255" t="s">
         <v>31</v>
       </c>
-      <c r="D255" s="2">
-        <v>1.8367472289166666E-2</v>
+      <c r="D255" s="6">
+        <v>1.84E-2</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
@@ -4172,8 +4295,8 @@
       <c r="C256" t="s">
         <v>31</v>
       </c>
-      <c r="D256" s="2">
-        <v>5.3941503686380225E-2</v>
+      <c r="D256" s="6">
+        <v>5.3900000000000003E-2</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
@@ -4186,8 +4309,8 @@
       <c r="C257" t="s">
         <v>31</v>
       </c>
-      <c r="D257" s="2">
-        <v>2.6456314435449754E-2</v>
+      <c r="D257" s="6">
+        <v>2.6499999999999999E-2</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
@@ -4195,12 +4318,12 @@
         <v>2</v>
       </c>
       <c r="B258" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C258" t="s">
         <v>31</v>
       </c>
-      <c r="D258" s="2">
+      <c r="D258" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4209,12 +4332,12 @@
         <v>3</v>
       </c>
       <c r="B259" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C259" t="s">
         <v>31</v>
       </c>
-      <c r="D259" s="2">
+      <c r="D259" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4223,12 +4346,12 @@
         <v>4</v>
       </c>
       <c r="B260" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C260" t="s">
         <v>31</v>
       </c>
-      <c r="D260" s="2">
+      <c r="D260" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4237,12 +4360,12 @@
         <v>5</v>
       </c>
       <c r="B261" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C261" t="s">
         <v>31</v>
       </c>
-      <c r="D261" s="2">
+      <c r="D261" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4251,12 +4374,12 @@
         <v>33</v>
       </c>
       <c r="B262" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C262" t="s">
         <v>31</v>
       </c>
-      <c r="D262" s="2">
+      <c r="D262" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4265,12 +4388,12 @@
         <v>6</v>
       </c>
       <c r="B263" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C263" t="s">
         <v>31</v>
       </c>
-      <c r="D263" s="2">
+      <c r="D263" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4279,12 +4402,12 @@
         <v>7</v>
       </c>
       <c r="B264" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C264" t="s">
         <v>31</v>
       </c>
-      <c r="D264" s="2">
+      <c r="D264" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4293,12 +4416,12 @@
         <v>8</v>
       </c>
       <c r="B265" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C265" t="s">
         <v>31</v>
       </c>
-      <c r="D265" s="2">
+      <c r="D265" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4307,12 +4430,12 @@
         <v>9</v>
       </c>
       <c r="B266" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C266" t="s">
         <v>31</v>
       </c>
-      <c r="D266" s="2">
+      <c r="D266" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4321,12 +4444,12 @@
         <v>10</v>
       </c>
       <c r="B267" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C267" t="s">
         <v>31</v>
       </c>
-      <c r="D267" s="2">
+      <c r="D267" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4335,12 +4458,12 @@
         <v>11</v>
       </c>
       <c r="B268" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C268" t="s">
         <v>31</v>
       </c>
-      <c r="D268" s="2">
+      <c r="D268" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4349,12 +4472,12 @@
         <v>12</v>
       </c>
       <c r="B269" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C269" t="s">
         <v>31</v>
       </c>
-      <c r="D269" s="2">
+      <c r="D269" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4363,12 +4486,12 @@
         <v>13</v>
       </c>
       <c r="B270" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C270" t="s">
         <v>31</v>
       </c>
-      <c r="D270" s="2">
+      <c r="D270" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4377,12 +4500,12 @@
         <v>14</v>
       </c>
       <c r="B271" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C271" t="s">
         <v>31</v>
       </c>
-      <c r="D271" s="2">
+      <c r="D271" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4391,12 +4514,12 @@
         <v>35</v>
       </c>
       <c r="B272" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C272" t="s">
         <v>31</v>
       </c>
-      <c r="D272" s="2">
+      <c r="D272" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4405,12 +4528,12 @@
         <v>34</v>
       </c>
       <c r="B273" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C273" t="s">
         <v>31</v>
       </c>
-      <c r="D273" s="2">
+      <c r="D273" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4419,12 +4542,12 @@
         <v>15</v>
       </c>
       <c r="B274" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C274" t="s">
         <v>31</v>
       </c>
-      <c r="D274" s="2">
+      <c r="D274" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4433,12 +4556,12 @@
         <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C275" t="s">
         <v>31</v>
       </c>
-      <c r="D275" s="2">
+      <c r="D275" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4447,12 +4570,12 @@
         <v>17</v>
       </c>
       <c r="B276" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C276" t="s">
         <v>31</v>
       </c>
-      <c r="D276" s="2">
+      <c r="D276" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4461,12 +4584,12 @@
         <v>18</v>
       </c>
       <c r="B277" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C277" t="s">
         <v>31</v>
       </c>
-      <c r="D277" s="2">
+      <c r="D277" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4475,12 +4598,12 @@
         <v>19</v>
       </c>
       <c r="B278" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C278" t="s">
         <v>31</v>
       </c>
-      <c r="D278" s="2">
+      <c r="D278" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4489,12 +4612,12 @@
         <v>20</v>
       </c>
       <c r="B279" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C279" t="s">
         <v>31</v>
       </c>
-      <c r="D279" s="2">
+      <c r="D279" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4503,12 +4626,12 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C280" t="s">
         <v>31</v>
       </c>
-      <c r="D280" s="2">
+      <c r="D280" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4517,12 +4640,12 @@
         <v>22</v>
       </c>
       <c r="B281" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C281" t="s">
         <v>31</v>
       </c>
-      <c r="D281" s="2">
+      <c r="D281" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4531,12 +4654,12 @@
         <v>23</v>
       </c>
       <c r="B282" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C282" t="s">
         <v>31</v>
       </c>
-      <c r="D282" s="2">
+      <c r="D282" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4545,12 +4668,12 @@
         <v>24</v>
       </c>
       <c r="B283" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C283" t="s">
         <v>31</v>
       </c>
-      <c r="D283" s="2">
+      <c r="D283" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4559,12 +4682,12 @@
         <v>25</v>
       </c>
       <c r="B284" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C284" t="s">
         <v>31</v>
       </c>
-      <c r="D284" s="2">
+      <c r="D284" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4573,12 +4696,12 @@
         <v>26</v>
       </c>
       <c r="B285" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C285" t="s">
         <v>31</v>
       </c>
-      <c r="D285" s="2">
+      <c r="D285" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4587,12 +4710,12 @@
         <v>27</v>
       </c>
       <c r="B286" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C286" t="s">
         <v>31</v>
       </c>
-      <c r="D286" s="2">
+      <c r="D286" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4601,12 +4724,12 @@
         <v>36</v>
       </c>
       <c r="B287" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C287" t="s">
         <v>31</v>
       </c>
-      <c r="D287" s="2">
+      <c r="D287" s="6">
         <v>0.05</v>
       </c>
     </row>
@@ -4615,12 +4738,12 @@
         <v>28</v>
       </c>
       <c r="B288" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C288" t="s">
         <v>31</v>
       </c>
-      <c r="D288" s="2">
+      <c r="D288" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4629,12 +4752,12 @@
         <v>29</v>
       </c>
       <c r="B289" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C289" t="s">
         <v>31</v>
       </c>
-      <c r="D289" s="2">
+      <c r="D289" s="6">
         <v>0</v>
       </c>
     </row>
@@ -4643,7 +4766,7 @@
         <v>2</v>
       </c>
       <c r="B290" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C290" t="s">
         <v>31</v>
@@ -4657,13 +4780,13 @@
         <v>3</v>
       </c>
       <c r="B291" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C291" t="s">
         <v>31</v>
       </c>
-      <c r="D291" s="2">
-        <v>1.2409953383107545E-2</v>
+      <c r="D291" s="6">
+        <v>4.3200000000000002E-2</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
@@ -4671,13 +4794,13 @@
         <v>4</v>
       </c>
       <c r="B292" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C292" t="s">
         <v>31</v>
       </c>
-      <c r="D292" s="2">
-        <v>4.7150096053842572E-2</v>
+      <c r="D292" s="6">
+        <v>1.24E-2</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
@@ -4685,13 +4808,13 @@
         <v>5</v>
       </c>
       <c r="B293" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C293" t="s">
         <v>31</v>
       </c>
-      <c r="D293" s="2">
-        <v>4.3009555726506582E-2</v>
+      <c r="D293" s="6">
+        <v>4.7199999999999999E-2</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
@@ -4699,13 +4822,13 @@
         <v>33</v>
       </c>
       <c r="B294" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C294" t="s">
         <v>31</v>
       </c>
-      <c r="D294" s="2">
-        <v>2.6465034006093947E-2</v>
+      <c r="D294" s="6">
+        <v>4.2999999999999997E-2</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
@@ -4713,13 +4836,13 @@
         <v>6</v>
       </c>
       <c r="B295" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C295" t="s">
         <v>31</v>
       </c>
-      <c r="D295" s="2">
-        <v>2.8076154821729433E-2</v>
+      <c r="D295" s="6">
+        <v>2.6499999999999999E-2</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
@@ -4727,13 +4850,13 @@
         <v>7</v>
       </c>
       <c r="B296" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C296" t="s">
         <v>31</v>
       </c>
-      <c r="D296" s="2">
-        <v>8.4370154521388463E-3</v>
+      <c r="D296" s="6">
+        <v>2.81E-2</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
@@ -4741,13 +4864,13 @@
         <v>8</v>
       </c>
       <c r="B297" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C297" t="s">
         <v>31</v>
       </c>
-      <c r="D297" s="2">
-        <v>0.05</v>
+      <c r="D297" s="6">
+        <v>8.3999999999999995E-3</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
@@ -4755,13 +4878,13 @@
         <v>9</v>
       </c>
       <c r="B298" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C298" t="s">
         <v>31</v>
       </c>
-      <c r="D298" s="2">
-        <v>2.5640594550740414E-2</v>
+      <c r="D298" s="6">
+        <v>0.05</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
@@ -4769,13 +4892,13 @@
         <v>10</v>
       </c>
       <c r="B299" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C299" t="s">
         <v>31</v>
       </c>
-      <c r="D299" s="2">
-        <v>2.2409785776028715E-2</v>
+      <c r="D299" s="6">
+        <v>2.5600000000000001E-2</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
@@ -4783,13 +4906,13 @@
         <v>11</v>
       </c>
       <c r="B300" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C300" t="s">
         <v>31</v>
       </c>
-      <c r="D300" s="2">
-        <v>2.9043241578945816E-2</v>
+      <c r="D300" s="6">
+        <v>2.24E-2</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
@@ -4797,13 +4920,13 @@
         <v>12</v>
       </c>
       <c r="B301" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C301" t="s">
         <v>31</v>
       </c>
-      <c r="D301" s="2">
-        <v>9.9882438863886647E-3</v>
+      <c r="D301" s="6">
+        <v>2.9000000000000001E-2</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
@@ -4811,13 +4934,13 @@
         <v>13</v>
       </c>
       <c r="B302" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C302" t="s">
         <v>31</v>
       </c>
-      <c r="D302" s="2">
-        <v>1.924274181335792E-2</v>
+      <c r="D302" s="6">
+        <v>0.01</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
@@ -4825,13 +4948,13 @@
         <v>14</v>
       </c>
       <c r="B303" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C303" t="s">
         <v>31</v>
       </c>
-      <c r="D303" s="2">
-        <v>4.0996397388314912E-3</v>
+      <c r="D303" s="6">
+        <v>1.9199999999999998E-2</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
@@ -4839,13 +4962,13 @@
         <v>35</v>
       </c>
       <c r="B304" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C304" t="s">
         <v>31</v>
       </c>
-      <c r="D304" s="2">
-        <v>1.8865393682225024E-2</v>
+      <c r="D304" s="6">
+        <v>4.1000000000000003E-3</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
@@ -4853,13 +4976,13 @@
         <v>34</v>
       </c>
       <c r="B305" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C305" t="s">
         <v>31</v>
       </c>
-      <c r="D305" s="2">
-        <v>7.6873495212079401E-3</v>
+      <c r="D305" s="6">
+        <v>1.89E-2</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
@@ -4867,13 +4990,13 @@
         <v>15</v>
       </c>
       <c r="B306" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C306" t="s">
         <v>31</v>
       </c>
-      <c r="D306" s="2">
-        <v>1.50448165412053E-2</v>
+      <c r="D306" s="6">
+        <v>7.7000000000000002E-3</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
@@ -4881,13 +5004,13 @@
         <v>16</v>
       </c>
       <c r="B307" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C307" t="s">
         <v>31</v>
       </c>
-      <c r="D307" s="2">
-        <v>1.9391292049054033E-2</v>
+      <c r="D307" s="6">
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
@@ -4895,13 +5018,13 @@
         <v>17</v>
       </c>
       <c r="B308" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C308" t="s">
         <v>31</v>
       </c>
-      <c r="D308" s="2">
-        <v>1.3411031336614537E-2</v>
+      <c r="D308" s="6">
+        <v>1.9400000000000001E-2</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
@@ -4909,13 +5032,13 @@
         <v>18</v>
       </c>
       <c r="B309" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C309" t="s">
         <v>31</v>
       </c>
-      <c r="D309" s="2">
-        <v>1.7117114539400836E-2</v>
+      <c r="D309" s="6">
+        <v>1.34E-2</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
@@ -4923,13 +5046,13 @@
         <v>19</v>
       </c>
       <c r="B310" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C310" t="s">
         <v>31</v>
       </c>
-      <c r="D310" s="2">
-        <v>8.6644808218048451E-3</v>
+      <c r="D310" s="6">
+        <v>1.7100000000000001E-2</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
@@ -4937,13 +5060,13 @@
         <v>20</v>
       </c>
       <c r="B311" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C311" t="s">
         <v>31</v>
       </c>
-      <c r="D311" s="2">
-        <v>2.3120042853282466E-2</v>
+      <c r="D311" s="6">
+        <v>8.6999999999999994E-3</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
@@ -4951,13 +5074,13 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C312" t="s">
         <v>31</v>
       </c>
-      <c r="D312" s="2">
-        <v>3.1928305887633186E-2</v>
+      <c r="D312" s="6">
+        <v>2.3099999999999999E-2</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
@@ -4965,13 +5088,13 @@
         <v>22</v>
       </c>
       <c r="B313" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C313" t="s">
         <v>31</v>
       </c>
-      <c r="D313" s="2">
-        <v>9.7012953359255916E-3</v>
+      <c r="D313" s="6">
+        <v>3.1899999999999998E-2</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
@@ -4979,13 +5102,13 @@
         <v>23</v>
       </c>
       <c r="B314" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C314" t="s">
         <v>31</v>
       </c>
-      <c r="D314" s="2">
-        <v>1.1306592686207125E-2</v>
+      <c r="D314" s="6">
+        <v>9.7000000000000003E-3</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
@@ -4993,13 +5116,13 @@
         <v>24</v>
       </c>
       <c r="B315" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C315" t="s">
         <v>31</v>
       </c>
-      <c r="D315" s="2">
-        <v>1.5495765060406612E-2</v>
+      <c r="D315" s="6">
+        <v>1.1299999999999999E-2</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
@@ -5007,13 +5130,13 @@
         <v>25</v>
       </c>
       <c r="B316" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C316" t="s">
         <v>31</v>
       </c>
-      <c r="D316" s="2">
-        <v>2.2316777428880389E-2</v>
+      <c r="D316" s="6">
+        <v>1.55E-2</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
@@ -5021,13 +5144,13 @@
         <v>26</v>
       </c>
       <c r="B317" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C317" t="s">
         <v>31</v>
       </c>
-      <c r="D317" s="2">
-        <v>1.6492593603295583E-2</v>
+      <c r="D317" s="6">
+        <v>2.23E-2</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
@@ -5035,13 +5158,13 @@
         <v>27</v>
       </c>
       <c r="B318" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C318" t="s">
         <v>31</v>
       </c>
-      <c r="D318" s="2">
-        <v>7.6451968094835244E-3</v>
+      <c r="D318" s="6">
+        <v>1.6500000000000001E-2</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
@@ -5049,13 +5172,13 @@
         <v>36</v>
       </c>
       <c r="B319" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C319" t="s">
         <v>31</v>
       </c>
-      <c r="D319" s="2">
-        <v>9.6216524423300871E-3</v>
+      <c r="D319" s="6">
+        <v>7.6E-3</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
@@ -5063,13 +5186,13 @@
         <v>28</v>
       </c>
       <c r="B320" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C320" t="s">
         <v>31</v>
       </c>
-      <c r="D320" s="2">
-        <v>1.720389271003156E-2</v>
+      <c r="D320" s="6">
+        <v>9.5999999999999992E-3</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
@@ -5077,13 +5200,13 @@
         <v>29</v>
       </c>
       <c r="B321" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C321" t="s">
         <v>31</v>
       </c>
-      <c r="D321" s="2">
-        <v>2.4614724630658322E-2</v>
+      <c r="D321" s="6">
+        <v>1.72E-2</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
@@ -5096,8 +5219,8 @@
       <c r="C322" t="s">
         <v>32</v>
       </c>
-      <c r="D322" s="2">
-        <v>7.183670252590914E-4</v>
+      <c r="D322">
+        <v>1.6299999999999999E-2</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
@@ -5110,8 +5233,8 @@
       <c r="C323" t="s">
         <v>32</v>
       </c>
-      <c r="D323" s="2">
-        <v>0</v>
+      <c r="D323">
+        <v>1.7600000000000001E-2</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
@@ -5124,8 +5247,8 @@
       <c r="C324" t="s">
         <v>32</v>
       </c>
-      <c r="D324" s="2">
-        <v>1.3355555962563421E-2</v>
+      <c r="D324">
+        <v>3.3799999999999997E-2</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
@@ -5138,8 +5261,8 @@
       <c r="C325" t="s">
         <v>32</v>
       </c>
-      <c r="D325" s="2">
-        <v>7.446150511820214E-2</v>
+      <c r="D325">
+        <v>5.6000000000000001E-2</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
@@ -5152,8 +5275,8 @@
       <c r="C326" t="s">
         <v>32</v>
       </c>
-      <c r="D326" s="2">
-        <v>0</v>
+      <c r="D326">
+        <v>1.11E-2</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
@@ -5166,8 +5289,8 @@
       <c r="C327" t="s">
         <v>32</v>
       </c>
-      <c r="D327" s="2">
-        <v>9.4480880496032628E-3</v>
+      <c r="D327">
+        <v>3.2599999999999997E-2</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
@@ -5180,8 +5303,8 @@
       <c r="C328" t="s">
         <v>32</v>
       </c>
-      <c r="D328" s="2">
-        <v>0</v>
+      <c r="D328">
+        <v>4.1999999999999997E-3</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
@@ -5194,8 +5317,8 @@
       <c r="C329" t="s">
         <v>32</v>
       </c>
-      <c r="D329" s="2">
-        <v>0</v>
+      <c r="D329">
+        <v>3.09E-2</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
@@ -5208,7 +5331,7 @@
       <c r="C330" t="s">
         <v>32</v>
       </c>
-      <c r="D330" s="2">
+      <c r="D330">
         <v>0.1</v>
       </c>
     </row>
@@ -5222,8 +5345,8 @@
       <c r="C331" t="s">
         <v>32</v>
       </c>
-      <c r="D331" s="2">
-        <v>0</v>
+      <c r="D331">
+        <v>1.6299999999999999E-2</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
@@ -5236,8 +5359,8 @@
       <c r="C332" t="s">
         <v>32</v>
       </c>
-      <c r="D332" s="2">
-        <v>9.1002348689251753E-3</v>
+      <c r="D332">
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
@@ -5250,8 +5373,8 @@
       <c r="C333" t="s">
         <v>32</v>
       </c>
-      <c r="D333" s="2">
-        <v>0</v>
+      <c r="D333">
+        <v>-2.8299999999999999E-2</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
@@ -5264,8 +5387,8 @@
       <c r="C334" t="s">
         <v>32</v>
       </c>
-      <c r="D334" s="2">
-        <v>1.8910858442718E-2</v>
+      <c r="D334">
+        <v>2.75E-2</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
@@ -5278,8 +5401,8 @@
       <c r="C335" t="s">
         <v>32</v>
       </c>
-      <c r="D335" s="2">
-        <v>3.2035286261554137E-3</v>
+      <c r="D335">
+        <v>1.47E-2</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
@@ -5292,8 +5415,8 @@
       <c r="C336" t="s">
         <v>32</v>
       </c>
-      <c r="D336" s="2">
-        <v>0</v>
+      <c r="D336">
+        <v>8.8000000000000005E-3</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
@@ -5306,8 +5429,8 @@
       <c r="C337" t="s">
         <v>32</v>
       </c>
-      <c r="D337" s="2">
-        <v>8.303366666742529E-4</v>
+      <c r="D337">
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
@@ -5320,8 +5443,8 @@
       <c r="C338" t="s">
         <v>32</v>
       </c>
-      <c r="D338" s="2">
-        <v>0</v>
+      <c r="D338">
+        <v>1.38E-2</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
@@ -5334,8 +5457,8 @@
       <c r="C339" t="s">
         <v>32</v>
       </c>
-      <c r="D339" s="2">
-        <v>-1.1853055916774887E-3</v>
+      <c r="D339">
+        <v>2.1399999999999999E-2</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
@@ -5348,8 +5471,8 @@
       <c r="C340" t="s">
         <v>32</v>
       </c>
-      <c r="D340" s="2">
-        <v>0</v>
+      <c r="D340">
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
@@ -5362,8 +5485,8 @@
       <c r="C341" t="s">
         <v>32</v>
       </c>
-      <c r="D341" s="2">
-        <v>7.990824213556033E-4</v>
+      <c r="D341">
+        <v>1.5299999999999999E-2</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
@@ -5376,8 +5499,8 @@
       <c r="C342" t="s">
         <v>32</v>
       </c>
-      <c r="D342" s="2">
-        <v>0</v>
+      <c r="D342">
+        <v>1.3899999999999999E-2</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
@@ -5390,8 +5513,8 @@
       <c r="C343" t="s">
         <v>32</v>
       </c>
-      <c r="D343" s="2">
-        <v>0</v>
+      <c r="D343">
+        <v>1.2999999999999999E-3</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
@@ -5404,8 +5527,8 @@
       <c r="C344" t="s">
         <v>32</v>
       </c>
-      <c r="D344" s="2">
-        <v>1.1891415321036432E-2</v>
+      <c r="D344">
+        <v>3.1E-2</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
@@ -5418,7 +5541,7 @@
       <c r="C345" t="s">
         <v>32</v>
       </c>
-      <c r="D345" s="2">
+      <c r="D345">
         <v>0</v>
       </c>
     </row>
@@ -5432,8 +5555,8 @@
       <c r="C346" t="s">
         <v>32</v>
       </c>
-      <c r="D346" s="2">
-        <v>0</v>
+      <c r="D346">
+        <v>3.7000000000000002E-3</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.2">
@@ -5446,8 +5569,8 @@
       <c r="C347" t="s">
         <v>32</v>
       </c>
-      <c r="D347" s="2">
-        <v>0</v>
+      <c r="D347">
+        <v>9.9000000000000008E-3</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.2">
@@ -5460,8 +5583,8 @@
       <c r="C348" t="s">
         <v>32</v>
       </c>
-      <c r="D348" s="2">
-        <v>1.2848841102195191E-3</v>
+      <c r="D348">
+        <v>2.1899999999999999E-2</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.2">
@@ -5474,8 +5597,8 @@
       <c r="C349" t="s">
         <v>32</v>
       </c>
-      <c r="D349" s="2">
-        <v>2.2505802373623692E-3</v>
+      <c r="D349">
+        <v>1.3599999999999999E-2</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.2">
@@ -5488,8 +5611,8 @@
       <c r="C350" t="s">
         <v>32</v>
       </c>
-      <c r="D350" s="2">
-        <v>8.3998034055886243E-3</v>
+      <c r="D350">
+        <v>1.8100000000000002E-2</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
@@ -5502,8 +5625,8 @@
       <c r="C351" t="s">
         <v>32</v>
       </c>
-      <c r="D351" s="2">
-        <v>-2.8087810229323419E-4</v>
+      <c r="D351">
+        <v>7.0000000000000001E-3</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.2">
@@ -5516,8 +5639,8 @@
       <c r="C352" t="s">
         <v>32</v>
       </c>
-      <c r="D352" s="2">
-        <v>0</v>
+      <c r="D352">
+        <v>1.8599999999999998E-2</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.2">
@@ -5530,8 +5653,8 @@
       <c r="C353" t="s">
         <v>32</v>
       </c>
-      <c r="D353" s="2">
-        <v>-5.0224813206674811E-4</v>
+      <c r="D353">
+        <v>1.9599999999999999E-2</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.2">
@@ -5545,7 +5668,7 @@
         <v>32</v>
       </c>
       <c r="D354" s="2">
-        <v>4.6364576026337603E-2</v>
+        <v>4.6399999999999997E-2</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.2">
@@ -5559,7 +5682,7 @@
         <v>32</v>
       </c>
       <c r="D355" s="2">
-        <v>6.2315699810072504E-2</v>
+        <v>6.2300000000000001E-2</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.2">
@@ -5573,7 +5696,7 @@
         <v>32</v>
       </c>
       <c r="D356" s="2">
-        <v>7.7311660163031176E-2</v>
+        <v>7.7299999999999994E-2</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.2">
@@ -5587,7 +5710,7 @@
         <v>32</v>
       </c>
       <c r="D357" s="2">
-        <v>7.6466674666716694E-3</v>
+        <v>7.6E-3</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.2">
@@ -5601,7 +5724,7 @@
         <v>32</v>
       </c>
       <c r="D358" s="2">
-        <v>1.4273336934953673E-2</v>
+        <v>1.43E-2</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.2">
@@ -5615,7 +5738,7 @@
         <v>32</v>
       </c>
       <c r="D359" s="2">
-        <v>1.3263213474543404E-2</v>
+        <v>1.3299999999999999E-2</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.2">
@@ -5629,7 +5752,7 @@
         <v>32</v>
       </c>
       <c r="D360" s="2">
-        <v>5.3827409720074881E-2</v>
+        <v>5.3800000000000001E-2</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.2">
@@ -5643,7 +5766,7 @@
         <v>32</v>
       </c>
       <c r="D361" s="2">
-        <v>3.6790428481495892E-2</v>
+        <v>3.6799999999999999E-2</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.2">
@@ -5657,7 +5780,7 @@
         <v>32</v>
       </c>
       <c r="D362" s="2">
-        <v>4.8350425387443878E-2</v>
+        <v>4.8399999999999999E-2</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
@@ -5671,7 +5794,7 @@
         <v>32</v>
       </c>
       <c r="D363" s="2">
-        <v>1.1370294815542463E-2</v>
+        <v>1.14E-2</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
@@ -5685,7 +5808,7 @@
         <v>32</v>
       </c>
       <c r="D364" s="2">
-        <v>7.3478463953109641E-2</v>
+        <v>7.3499999999999996E-2</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.2">
@@ -5699,7 +5822,7 @@
         <v>32</v>
       </c>
       <c r="D365" s="2">
-        <v>-1.4918924784331263E-3</v>
+        <v>-1.5E-3</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.2">
@@ -5713,7 +5836,7 @@
         <v>32</v>
       </c>
       <c r="D366" s="2">
-        <v>1.7964167513013121E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.2">
@@ -5727,7 +5850,7 @@
         <v>32</v>
       </c>
       <c r="D367" s="2">
-        <v>2.472100970521347E-2</v>
+        <v>2.47E-2</v>
       </c>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.2">
@@ -5755,7 +5878,7 @@
         <v>32</v>
       </c>
       <c r="D369" s="2">
-        <v>3.76984910708862E-2</v>
+        <v>3.7699999999999997E-2</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.2">
@@ -5769,7 +5892,7 @@
         <v>32</v>
       </c>
       <c r="D370" s="2">
-        <v>8.8254375977293201E-2</v>
+        <v>8.8300000000000003E-2</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.2">
@@ -5783,7 +5906,7 @@
         <v>32</v>
       </c>
       <c r="D371" s="2">
-        <v>7.5708639377810458E-2</v>
+        <v>7.5700000000000003E-2</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.2">
@@ -5797,7 +5920,7 @@
         <v>32</v>
       </c>
       <c r="D372" s="2">
-        <v>2.1451844997668237E-2</v>
+        <v>2.1499999999999998E-2</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.2">
@@ -5811,7 +5934,7 @@
         <v>32</v>
       </c>
       <c r="D373" s="2">
-        <v>3.2443648891790862E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.2">
@@ -5825,7 +5948,7 @@
         <v>32</v>
       </c>
       <c r="D374" s="2">
-        <v>2.0367445586154217E-2</v>
+        <v>2.0400000000000001E-2</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
@@ -5839,7 +5962,7 @@
         <v>32</v>
       </c>
       <c r="D375" s="2">
-        <v>7.1573671442384842E-2</v>
+        <v>7.1599999999999997E-2</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.2">
@@ -5853,7 +5976,7 @@
         <v>32</v>
       </c>
       <c r="D376" s="2">
-        <v>6.767266140934898E-2</v>
+        <v>6.7699999999999996E-2</v>
       </c>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
@@ -5867,7 +5990,7 @@
         <v>32</v>
       </c>
       <c r="D377" s="2">
-        <v>0</v>
+        <v>-6.6E-3</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.2">
@@ -5881,7 +6004,7 @@
         <v>32</v>
       </c>
       <c r="D378" s="2">
-        <v>2.9772692907791248E-2</v>
+        <v>2.98E-2</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.2">
@@ -5895,7 +6018,7 @@
         <v>32</v>
       </c>
       <c r="D379" s="2">
-        <v>3.636158506637753E-2</v>
+        <v>3.6400000000000002E-2</v>
       </c>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.2">
@@ -5909,7 +6032,7 @@
         <v>32</v>
       </c>
       <c r="D380" s="2">
-        <v>8.0502394236473904E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.2">
@@ -5923,7 +6046,7 @@
         <v>32</v>
       </c>
       <c r="D381" s="2">
-        <v>0</v>
+        <v>-2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.2">
@@ -5937,7 +6060,7 @@
         <v>32</v>
       </c>
       <c r="D382" s="2">
-        <v>3.742444529773032E-2</v>
+        <v>3.7400000000000003E-2</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.2">
@@ -5951,7 +6074,7 @@
         <v>32</v>
       </c>
       <c r="D383" s="2">
-        <v>2.9025926867355369E-2</v>
+        <v>2.9000000000000001E-2</v>
       </c>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.2">
@@ -5965,7 +6088,7 @@
         <v>32</v>
       </c>
       <c r="D384" s="2">
-        <v>7.4472553320996801E-3</v>
+        <v>7.4000000000000003E-3</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.2">
@@ -5979,7 +6102,7 @@
         <v>32</v>
       </c>
       <c r="D385" s="2">
-        <v>2.6857824197253671E-2</v>
+        <v>2.69E-2</v>
       </c>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.2">
@@ -5987,7 +6110,7 @@
         <v>2</v>
       </c>
       <c r="B386" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C386" t="s">
         <v>32</v>
@@ -6001,7 +6124,7 @@
         <v>3</v>
       </c>
       <c r="B387" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C387" t="s">
         <v>32</v>
@@ -6015,7 +6138,7 @@
         <v>4</v>
       </c>
       <c r="B388" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C388" t="s">
         <v>32</v>
@@ -6029,7 +6152,7 @@
         <v>5</v>
       </c>
       <c r="B389" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C389" t="s">
         <v>32</v>
@@ -6043,7 +6166,7 @@
         <v>33</v>
       </c>
       <c r="B390" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C390" t="s">
         <v>32</v>
@@ -6057,7 +6180,7 @@
         <v>6</v>
       </c>
       <c r="B391" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C391" t="s">
         <v>32</v>
@@ -6071,7 +6194,7 @@
         <v>7</v>
       </c>
       <c r="B392" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C392" t="s">
         <v>32</v>
@@ -6085,7 +6208,7 @@
         <v>8</v>
       </c>
       <c r="B393" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C393" t="s">
         <v>32</v>
@@ -6099,7 +6222,7 @@
         <v>9</v>
       </c>
       <c r="B394" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C394" t="s">
         <v>32</v>
@@ -6113,7 +6236,7 @@
         <v>10</v>
       </c>
       <c r="B395" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C395" t="s">
         <v>32</v>
@@ -6127,7 +6250,7 @@
         <v>11</v>
       </c>
       <c r="B396" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C396" t="s">
         <v>32</v>
@@ -6141,7 +6264,7 @@
         <v>12</v>
       </c>
       <c r="B397" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C397" t="s">
         <v>32</v>
@@ -6155,7 +6278,7 @@
         <v>13</v>
       </c>
       <c r="B398" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C398" t="s">
         <v>32</v>
@@ -6169,7 +6292,7 @@
         <v>14</v>
       </c>
       <c r="B399" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C399" t="s">
         <v>32</v>
@@ -6183,7 +6306,7 @@
         <v>35</v>
       </c>
       <c r="B400" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C400" t="s">
         <v>32</v>
@@ -6197,7 +6320,7 @@
         <v>34</v>
       </c>
       <c r="B401" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C401" t="s">
         <v>32</v>
@@ -6211,7 +6334,7 @@
         <v>15</v>
       </c>
       <c r="B402" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C402" t="s">
         <v>32</v>
@@ -6225,7 +6348,7 @@
         <v>16</v>
       </c>
       <c r="B403" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C403" t="s">
         <v>32</v>
@@ -6239,7 +6362,7 @@
         <v>17</v>
       </c>
       <c r="B404" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C404" t="s">
         <v>32</v>
@@ -6253,7 +6376,7 @@
         <v>18</v>
       </c>
       <c r="B405" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C405" t="s">
         <v>32</v>
@@ -6267,7 +6390,7 @@
         <v>19</v>
       </c>
       <c r="B406" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C406" t="s">
         <v>32</v>
@@ -6281,7 +6404,7 @@
         <v>20</v>
       </c>
       <c r="B407" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C407" t="s">
         <v>32</v>
@@ -6295,7 +6418,7 @@
         <v>21</v>
       </c>
       <c r="B408" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C408" t="s">
         <v>32</v>
@@ -6309,7 +6432,7 @@
         <v>22</v>
       </c>
       <c r="B409" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C409" t="s">
         <v>32</v>
@@ -6323,7 +6446,7 @@
         <v>23</v>
       </c>
       <c r="B410" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C410" t="s">
         <v>32</v>
@@ -6337,7 +6460,7 @@
         <v>24</v>
       </c>
       <c r="B411" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C411" t="s">
         <v>32</v>
@@ -6351,7 +6474,7 @@
         <v>25</v>
       </c>
       <c r="B412" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C412" t="s">
         <v>32</v>
@@ -6365,7 +6488,7 @@
         <v>26</v>
       </c>
       <c r="B413" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C413" t="s">
         <v>32</v>
@@ -6379,7 +6502,7 @@
         <v>27</v>
       </c>
       <c r="B414" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C414" t="s">
         <v>32</v>
@@ -6393,7 +6516,7 @@
         <v>36</v>
       </c>
       <c r="B415" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C415" t="s">
         <v>32</v>
@@ -6407,7 +6530,7 @@
         <v>28</v>
       </c>
       <c r="B416" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C416" t="s">
         <v>32</v>
@@ -6421,7 +6544,7 @@
         <v>29</v>
       </c>
       <c r="B417" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C417" t="s">
         <v>32</v>
@@ -6435,7 +6558,7 @@
         <v>2</v>
       </c>
       <c r="B418" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C418" t="s">
         <v>32</v>
@@ -6449,7 +6572,7 @@
         <v>3</v>
       </c>
       <c r="B419" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C419" t="s">
         <v>32</v>
@@ -6463,7 +6586,7 @@
         <v>4</v>
       </c>
       <c r="B420" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C420" t="s">
         <v>32</v>
@@ -6477,7 +6600,7 @@
         <v>5</v>
       </c>
       <c r="B421" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C421" t="s">
         <v>32</v>
@@ -6491,7 +6614,7 @@
         <v>33</v>
       </c>
       <c r="B422" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C422" t="s">
         <v>32</v>
@@ -6505,7 +6628,7 @@
         <v>6</v>
       </c>
       <c r="B423" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C423" t="s">
         <v>32</v>
@@ -6519,7 +6642,7 @@
         <v>7</v>
       </c>
       <c r="B424" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C424" t="s">
         <v>32</v>
@@ -6533,7 +6656,7 @@
         <v>8</v>
       </c>
       <c r="B425" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C425" t="s">
         <v>32</v>
@@ -6547,7 +6670,7 @@
         <v>9</v>
       </c>
       <c r="B426" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C426" t="s">
         <v>32</v>
@@ -6561,7 +6684,7 @@
         <v>10</v>
       </c>
       <c r="B427" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C427" t="s">
         <v>32</v>
@@ -6575,7 +6698,7 @@
         <v>11</v>
       </c>
       <c r="B428" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C428" t="s">
         <v>32</v>
@@ -6589,7 +6712,7 @@
         <v>12</v>
       </c>
       <c r="B429" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C429" t="s">
         <v>32</v>
@@ -6603,7 +6726,7 @@
         <v>13</v>
       </c>
       <c r="B430" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C430" t="s">
         <v>32</v>
@@ -6617,7 +6740,7 @@
         <v>14</v>
       </c>
       <c r="B431" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C431" t="s">
         <v>32</v>
@@ -6631,7 +6754,7 @@
         <v>35</v>
       </c>
       <c r="B432" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C432" t="s">
         <v>32</v>
@@ -6645,7 +6768,7 @@
         <v>34</v>
       </c>
       <c r="B433" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C433" t="s">
         <v>32</v>
@@ -6659,7 +6782,7 @@
         <v>15</v>
       </c>
       <c r="B434" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C434" t="s">
         <v>32</v>
@@ -6673,7 +6796,7 @@
         <v>16</v>
       </c>
       <c r="B435" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C435" t="s">
         <v>32</v>
@@ -6687,7 +6810,7 @@
         <v>17</v>
       </c>
       <c r="B436" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C436" t="s">
         <v>32</v>
@@ -6701,7 +6824,7 @@
         <v>18</v>
       </c>
       <c r="B437" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C437" t="s">
         <v>32</v>
@@ -6715,7 +6838,7 @@
         <v>19</v>
       </c>
       <c r="B438" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C438" t="s">
         <v>32</v>
@@ -6729,7 +6852,7 @@
         <v>20</v>
       </c>
       <c r="B439" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C439" t="s">
         <v>32</v>
@@ -6743,7 +6866,7 @@
         <v>21</v>
       </c>
       <c r="B440" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C440" t="s">
         <v>32</v>
@@ -6757,7 +6880,7 @@
         <v>22</v>
       </c>
       <c r="B441" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C441" t="s">
         <v>32</v>
@@ -6771,7 +6894,7 @@
         <v>23</v>
       </c>
       <c r="B442" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C442" t="s">
         <v>32</v>
@@ -6785,7 +6908,7 @@
         <v>24</v>
       </c>
       <c r="B443" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C443" t="s">
         <v>32</v>
@@ -6799,7 +6922,7 @@
         <v>25</v>
       </c>
       <c r="B444" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C444" t="s">
         <v>32</v>
@@ -6813,7 +6936,7 @@
         <v>26</v>
       </c>
       <c r="B445" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C445" t="s">
         <v>32</v>
@@ -6827,7 +6950,7 @@
         <v>27</v>
       </c>
       <c r="B446" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C446" t="s">
         <v>32</v>
@@ -6841,7 +6964,7 @@
         <v>36</v>
       </c>
       <c r="B447" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C447" t="s">
         <v>32</v>
@@ -6855,7 +6978,7 @@
         <v>28</v>
       </c>
       <c r="B448" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C448" t="s">
         <v>32</v>
@@ -6869,7 +6992,7 @@
         <v>29</v>
       </c>
       <c r="B449" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C449" t="s">
         <v>32</v>
@@ -6883,7 +7006,7 @@
         <v>2</v>
       </c>
       <c r="B450" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C450" t="s">
         <v>32</v>
@@ -6897,7 +7020,7 @@
         <v>3</v>
       </c>
       <c r="B451" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C451" t="s">
         <v>32</v>
@@ -6911,7 +7034,7 @@
         <v>4</v>
       </c>
       <c r="B452" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C452" t="s">
         <v>32</v>
@@ -6925,7 +7048,7 @@
         <v>5</v>
       </c>
       <c r="B453" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C453" t="s">
         <v>32</v>
@@ -6939,7 +7062,7 @@
         <v>33</v>
       </c>
       <c r="B454" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C454" t="s">
         <v>32</v>
@@ -6953,7 +7076,7 @@
         <v>6</v>
       </c>
       <c r="B455" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C455" t="s">
         <v>32</v>
@@ -6967,7 +7090,7 @@
         <v>7</v>
       </c>
       <c r="B456" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C456" t="s">
         <v>32</v>
@@ -6981,7 +7104,7 @@
         <v>8</v>
       </c>
       <c r="B457" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C457" t="s">
         <v>32</v>
@@ -6995,7 +7118,7 @@
         <v>9</v>
       </c>
       <c r="B458" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C458" t="s">
         <v>32</v>
@@ -7009,7 +7132,7 @@
         <v>10</v>
       </c>
       <c r="B459" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C459" t="s">
         <v>32</v>
@@ -7023,7 +7146,7 @@
         <v>11</v>
       </c>
       <c r="B460" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C460" t="s">
         <v>32</v>
@@ -7037,7 +7160,7 @@
         <v>12</v>
       </c>
       <c r="B461" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C461" t="s">
         <v>32</v>
@@ -7051,7 +7174,7 @@
         <v>13</v>
       </c>
       <c r="B462" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C462" t="s">
         <v>32</v>
@@ -7065,7 +7188,7 @@
         <v>14</v>
       </c>
       <c r="B463" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C463" t="s">
         <v>32</v>
@@ -7079,7 +7202,7 @@
         <v>35</v>
       </c>
       <c r="B464" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C464" t="s">
         <v>32</v>
@@ -7093,7 +7216,7 @@
         <v>34</v>
       </c>
       <c r="B465" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C465" t="s">
         <v>32</v>
@@ -7107,7 +7230,7 @@
         <v>15</v>
       </c>
       <c r="B466" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C466" t="s">
         <v>32</v>
@@ -7121,7 +7244,7 @@
         <v>16</v>
       </c>
       <c r="B467" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C467" t="s">
         <v>32</v>
@@ -7135,7 +7258,7 @@
         <v>17</v>
       </c>
       <c r="B468" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C468" t="s">
         <v>32</v>
@@ -7149,7 +7272,7 @@
         <v>18</v>
       </c>
       <c r="B469" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C469" t="s">
         <v>32</v>
@@ -7163,7 +7286,7 @@
         <v>19</v>
       </c>
       <c r="B470" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C470" t="s">
         <v>32</v>
@@ -7177,7 +7300,7 @@
         <v>20</v>
       </c>
       <c r="B471" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C471" t="s">
         <v>32</v>
@@ -7191,7 +7314,7 @@
         <v>21</v>
       </c>
       <c r="B472" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C472" t="s">
         <v>32</v>
@@ -7205,7 +7328,7 @@
         <v>22</v>
       </c>
       <c r="B473" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C473" t="s">
         <v>32</v>
@@ -7219,7 +7342,7 @@
         <v>23</v>
       </c>
       <c r="B474" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C474" t="s">
         <v>32</v>
@@ -7233,7 +7356,7 @@
         <v>24</v>
       </c>
       <c r="B475" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C475" t="s">
         <v>32</v>
@@ -7247,7 +7370,7 @@
         <v>25</v>
       </c>
       <c r="B476" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C476" t="s">
         <v>32</v>
@@ -7261,7 +7384,7 @@
         <v>26</v>
       </c>
       <c r="B477" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C477" t="s">
         <v>32</v>
@@ -7275,7 +7398,7 @@
         <v>27</v>
       </c>
       <c r="B478" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C478" t="s">
         <v>32</v>
@@ -7289,7 +7412,7 @@
         <v>36</v>
       </c>
       <c r="B479" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C479" t="s">
         <v>32</v>
@@ -7303,7 +7426,7 @@
         <v>28</v>
       </c>
       <c r="B480" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C480" t="s">
         <v>32</v>
@@ -7317,7 +7440,7 @@
         <v>29</v>
       </c>
       <c r="B481" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C481" t="s">
         <v>32</v>
@@ -7331,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="B482" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C482" t="s">
         <v>32</v>
@@ -7345,7 +7468,7 @@
         <v>3</v>
       </c>
       <c r="B483" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C483" t="s">
         <v>32</v>
@@ -7359,7 +7482,7 @@
         <v>4</v>
       </c>
       <c r="B484" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C484" t="s">
         <v>32</v>
@@ -7373,7 +7496,7 @@
         <v>5</v>
       </c>
       <c r="B485" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C485" t="s">
         <v>32</v>
@@ -7387,7 +7510,7 @@
         <v>33</v>
       </c>
       <c r="B486" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C486" t="s">
         <v>32</v>
@@ -7401,7 +7524,7 @@
         <v>6</v>
       </c>
       <c r="B487" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C487" t="s">
         <v>32</v>
@@ -7415,7 +7538,7 @@
         <v>7</v>
       </c>
       <c r="B488" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C488" t="s">
         <v>32</v>
@@ -7429,7 +7552,7 @@
         <v>8</v>
       </c>
       <c r="B489" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C489" t="s">
         <v>32</v>
@@ -7443,7 +7566,7 @@
         <v>9</v>
       </c>
       <c r="B490" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C490" t="s">
         <v>32</v>
@@ -7457,7 +7580,7 @@
         <v>10</v>
       </c>
       <c r="B491" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C491" t="s">
         <v>32</v>
@@ -7471,7 +7594,7 @@
         <v>11</v>
       </c>
       <c r="B492" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C492" t="s">
         <v>32</v>
@@ -7485,7 +7608,7 @@
         <v>12</v>
       </c>
       <c r="B493" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C493" t="s">
         <v>32</v>
@@ -7499,7 +7622,7 @@
         <v>13</v>
       </c>
       <c r="B494" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C494" t="s">
         <v>32</v>
@@ -7513,7 +7636,7 @@
         <v>14</v>
       </c>
       <c r="B495" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C495" t="s">
         <v>32</v>
@@ -7527,7 +7650,7 @@
         <v>35</v>
       </c>
       <c r="B496" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C496" t="s">
         <v>32</v>
@@ -7541,7 +7664,7 @@
         <v>34</v>
       </c>
       <c r="B497" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C497" t="s">
         <v>32</v>
@@ -7555,7 +7678,7 @@
         <v>15</v>
       </c>
       <c r="B498" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C498" t="s">
         <v>32</v>
@@ -7569,7 +7692,7 @@
         <v>16</v>
       </c>
       <c r="B499" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C499" t="s">
         <v>32</v>
@@ -7583,7 +7706,7 @@
         <v>17</v>
       </c>
       <c r="B500" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C500" t="s">
         <v>32</v>
@@ -7597,7 +7720,7 @@
         <v>18</v>
       </c>
       <c r="B501" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C501" t="s">
         <v>32</v>
@@ -7611,7 +7734,7 @@
         <v>19</v>
       </c>
       <c r="B502" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C502" t="s">
         <v>32</v>
@@ -7625,7 +7748,7 @@
         <v>20</v>
       </c>
       <c r="B503" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C503" t="s">
         <v>32</v>
@@ -7639,7 +7762,7 @@
         <v>21</v>
       </c>
       <c r="B504" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C504" t="s">
         <v>32</v>
@@ -7653,7 +7776,7 @@
         <v>22</v>
       </c>
       <c r="B505" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C505" t="s">
         <v>32</v>
@@ -7667,7 +7790,7 @@
         <v>23</v>
       </c>
       <c r="B506" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C506" t="s">
         <v>32</v>
@@ -7681,7 +7804,7 @@
         <v>24</v>
       </c>
       <c r="B507" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C507" t="s">
         <v>32</v>
@@ -7695,7 +7818,7 @@
         <v>25</v>
       </c>
       <c r="B508" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C508" t="s">
         <v>32</v>
@@ -7709,7 +7832,7 @@
         <v>26</v>
       </c>
       <c r="B509" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C509" t="s">
         <v>32</v>
@@ -7723,7 +7846,7 @@
         <v>27</v>
       </c>
       <c r="B510" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C510" t="s">
         <v>32</v>
@@ -7737,7 +7860,7 @@
         <v>36</v>
       </c>
       <c r="B511" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C511" t="s">
         <v>32</v>
@@ -7751,7 +7874,7 @@
         <v>28</v>
       </c>
       <c r="B512" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C512" t="s">
         <v>32</v>
@@ -7765,7 +7888,7 @@
         <v>29</v>
       </c>
       <c r="B513" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C513" t="s">
         <v>32</v>
@@ -7779,7 +7902,7 @@
         <v>2</v>
       </c>
       <c r="B514" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C514" t="s">
         <v>32</v>
@@ -7793,7 +7916,7 @@
         <v>3</v>
       </c>
       <c r="B515" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C515" t="s">
         <v>32</v>
@@ -7807,7 +7930,7 @@
         <v>4</v>
       </c>
       <c r="B516" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C516" t="s">
         <v>32</v>
@@ -7821,7 +7944,7 @@
         <v>5</v>
       </c>
       <c r="B517" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C517" t="s">
         <v>32</v>
@@ -7835,7 +7958,7 @@
         <v>33</v>
       </c>
       <c r="B518" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C518" t="s">
         <v>32</v>
@@ -7849,7 +7972,7 @@
         <v>6</v>
       </c>
       <c r="B519" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C519" t="s">
         <v>32</v>
@@ -7863,7 +7986,7 @@
         <v>7</v>
       </c>
       <c r="B520" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C520" t="s">
         <v>32</v>
@@ -7877,7 +8000,7 @@
         <v>8</v>
       </c>
       <c r="B521" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C521" t="s">
         <v>32</v>
@@ -7891,7 +8014,7 @@
         <v>9</v>
       </c>
       <c r="B522" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C522" t="s">
         <v>32</v>
@@ -7905,7 +8028,7 @@
         <v>10</v>
       </c>
       <c r="B523" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C523" t="s">
         <v>32</v>
@@ -7919,7 +8042,7 @@
         <v>11</v>
       </c>
       <c r="B524" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C524" t="s">
         <v>32</v>
@@ -7933,7 +8056,7 @@
         <v>12</v>
       </c>
       <c r="B525" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C525" t="s">
         <v>32</v>
@@ -7947,7 +8070,7 @@
         <v>13</v>
       </c>
       <c r="B526" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C526" t="s">
         <v>32</v>
@@ -7961,7 +8084,7 @@
         <v>14</v>
       </c>
       <c r="B527" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C527" t="s">
         <v>32</v>
@@ -7975,7 +8098,7 @@
         <v>35</v>
       </c>
       <c r="B528" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C528" t="s">
         <v>32</v>
@@ -7989,7 +8112,7 @@
         <v>34</v>
       </c>
       <c r="B529" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C529" t="s">
         <v>32</v>
@@ -8003,7 +8126,7 @@
         <v>15</v>
       </c>
       <c r="B530" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C530" t="s">
         <v>32</v>
@@ -8017,7 +8140,7 @@
         <v>16</v>
       </c>
       <c r="B531" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C531" t="s">
         <v>32</v>
@@ -8031,7 +8154,7 @@
         <v>17</v>
       </c>
       <c r="B532" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C532" t="s">
         <v>32</v>
@@ -8045,7 +8168,7 @@
         <v>18</v>
       </c>
       <c r="B533" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C533" t="s">
         <v>32</v>
@@ -8059,7 +8182,7 @@
         <v>19</v>
       </c>
       <c r="B534" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C534" t="s">
         <v>32</v>
@@ -8073,7 +8196,7 @@
         <v>20</v>
       </c>
       <c r="B535" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C535" t="s">
         <v>32</v>
@@ -8087,7 +8210,7 @@
         <v>21</v>
       </c>
       <c r="B536" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C536" t="s">
         <v>32</v>
@@ -8101,7 +8224,7 @@
         <v>22</v>
       </c>
       <c r="B537" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C537" t="s">
         <v>32</v>
@@ -8115,7 +8238,7 @@
         <v>23</v>
       </c>
       <c r="B538" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C538" t="s">
         <v>32</v>
@@ -8129,7 +8252,7 @@
         <v>24</v>
       </c>
       <c r="B539" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C539" t="s">
         <v>32</v>
@@ -8143,7 +8266,7 @@
         <v>25</v>
       </c>
       <c r="B540" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C540" t="s">
         <v>32</v>
@@ -8157,7 +8280,7 @@
         <v>26</v>
       </c>
       <c r="B541" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C541" t="s">
         <v>32</v>
@@ -8171,7 +8294,7 @@
         <v>27</v>
       </c>
       <c r="B542" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C542" t="s">
         <v>32</v>
@@ -8185,7 +8308,7 @@
         <v>36</v>
       </c>
       <c r="B543" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C543" t="s">
         <v>32</v>
@@ -8199,7 +8322,7 @@
         <v>28</v>
       </c>
       <c r="B544" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C544" t="s">
         <v>32</v>
@@ -8213,7 +8336,7 @@
         <v>29</v>
       </c>
       <c r="B545" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C545" t="s">
         <v>32</v>
@@ -8227,13 +8350,13 @@
         <v>2</v>
       </c>
       <c r="B546" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C546" t="s">
         <v>32</v>
       </c>
       <c r="D546" s="2">
-        <v>1.2143221451932251E-2</v>
+        <v>1.21E-2</v>
       </c>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.2">
@@ -8241,13 +8364,13 @@
         <v>3</v>
       </c>
       <c r="B547" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C547" t="s">
         <v>32</v>
       </c>
       <c r="D547" s="2">
-        <v>1.2560704848371891E-2</v>
+        <v>1.26E-2</v>
       </c>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.2">
@@ -8255,7 +8378,7 @@
         <v>4</v>
       </c>
       <c r="B548" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C548" t="s">
         <v>32</v>
@@ -8269,13 +8392,13 @@
         <v>5</v>
       </c>
       <c r="B549" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C549" t="s">
         <v>32</v>
       </c>
       <c r="D549" s="2">
-        <v>2.7400111333090747E-2</v>
+        <v>2.7400000000000001E-2</v>
       </c>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.2">
@@ -8283,13 +8406,13 @@
         <v>33</v>
       </c>
       <c r="B550" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C550" t="s">
         <v>32</v>
       </c>
       <c r="D550" s="2">
-        <v>3.7162122359095433E-2</v>
+        <v>3.7199999999999997E-2</v>
       </c>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.2">
@@ -8297,13 +8420,13 @@
         <v>6</v>
       </c>
       <c r="B551" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C551" t="s">
         <v>32</v>
       </c>
       <c r="D551" s="2">
-        <v>4.8787595700630237E-2</v>
+        <v>4.8800000000000003E-2</v>
       </c>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.2">
@@ -8311,13 +8434,13 @@
         <v>7</v>
       </c>
       <c r="B552" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C552" t="s">
         <v>32</v>
       </c>
       <c r="D552" s="2">
-        <v>7.1374968464491756E-3</v>
+        <v>7.1000000000000004E-3</v>
       </c>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.2">
@@ -8325,13 +8448,13 @@
         <v>8</v>
       </c>
       <c r="B553" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C553" t="s">
         <v>32</v>
       </c>
       <c r="D553" s="2">
-        <v>1.6995016098587449E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.2">
@@ -8339,13 +8462,13 @@
         <v>9</v>
       </c>
       <c r="B554" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C554" t="s">
         <v>32</v>
       </c>
       <c r="D554" s="2">
-        <v>1.8412887604616725E-3</v>
+        <v>1.8E-3</v>
       </c>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.2">
@@ -8353,13 +8476,13 @@
         <v>10</v>
       </c>
       <c r="B555" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C555" t="s">
         <v>32</v>
       </c>
       <c r="D555" s="2">
-        <v>8.4822447497929047E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.2">
@@ -8367,13 +8490,13 @@
         <v>11</v>
       </c>
       <c r="B556" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C556" t="s">
         <v>32</v>
       </c>
       <c r="D556" s="2">
-        <v>1.8275069482685032E-2</v>
+        <v>1.83E-2</v>
       </c>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.2">
@@ -8381,13 +8504,13 @@
         <v>12</v>
       </c>
       <c r="B557" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C557" t="s">
         <v>32</v>
       </c>
       <c r="D557" s="2">
-        <v>8.0823077320384025E-3</v>
+        <v>8.0999999999999996E-3</v>
       </c>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.2">
@@ -8395,13 +8518,13 @@
         <v>13</v>
       </c>
       <c r="B558" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C558" t="s">
         <v>32</v>
       </c>
       <c r="D558" s="2">
-        <v>6.303027726984608E-3</v>
+        <v>6.3E-3</v>
       </c>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.2">
@@ -8409,13 +8532,13 @@
         <v>14</v>
       </c>
       <c r="B559" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C559" t="s">
         <v>32</v>
       </c>
       <c r="D559" s="2">
-        <v>1.9594236671111605E-2</v>
+        <v>1.9599999999999999E-2</v>
       </c>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.2">
@@ -8423,13 +8546,13 @@
         <v>35</v>
       </c>
       <c r="B560" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C560" t="s">
         <v>32</v>
       </c>
       <c r="D560" s="2">
-        <v>3.014744237564519E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.2">
@@ -8437,13 +8560,13 @@
         <v>34</v>
       </c>
       <c r="B561" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C561" t="s">
         <v>32</v>
       </c>
       <c r="D561" s="2">
-        <v>8.5555396543679739E-3</v>
+        <v>8.6E-3</v>
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.2">
@@ -8451,13 +8574,13 @@
         <v>15</v>
       </c>
       <c r="B562" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C562" t="s">
         <v>32</v>
       </c>
       <c r="D562" s="2">
-        <v>1.4156749861389012E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.2">
@@ -8465,13 +8588,13 @@
         <v>16</v>
       </c>
       <c r="B563" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C563" t="s">
         <v>32</v>
       </c>
       <c r="D563" s="2">
-        <v>2.3163031101239052E-2</v>
+        <v>2.3199999999999998E-2</v>
       </c>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.2">
@@ -8479,13 +8602,13 @@
         <v>17</v>
       </c>
       <c r="B564" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C564" t="s">
         <v>32</v>
       </c>
       <c r="D564" s="2">
-        <v>4.3975286739018436E-3</v>
+        <v>4.4000000000000003E-3</v>
       </c>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.2">
@@ -8493,13 +8616,13 @@
         <v>18</v>
       </c>
       <c r="B565" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C565" t="s">
         <v>32</v>
       </c>
       <c r="D565" s="2">
-        <v>1.2824872175804067E-3</v>
+        <v>1.2999999999999999E-3</v>
       </c>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.2">
@@ -8507,13 +8630,13 @@
         <v>19</v>
       </c>
       <c r="B566" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C566" t="s">
         <v>32</v>
       </c>
       <c r="D566" s="2">
-        <v>1.2611400611472015E-2</v>
+        <v>1.26E-2</v>
       </c>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.2">
@@ -8521,13 +8644,13 @@
         <v>20</v>
       </c>
       <c r="B567" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C567" t="s">
         <v>32</v>
       </c>
       <c r="D567" s="2">
-        <v>6.5633111378406222E-3</v>
+        <v>6.6E-3</v>
       </c>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.2">
@@ -8535,13 +8658,13 @@
         <v>21</v>
       </c>
       <c r="B568" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C568" t="s">
         <v>32</v>
       </c>
       <c r="D568" s="2">
-        <v>7.6059846068372537E-3</v>
+        <v>7.6E-3</v>
       </c>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.2">
@@ -8549,13 +8672,13 @@
         <v>22</v>
       </c>
       <c r="B569" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C569" t="s">
         <v>32</v>
       </c>
       <c r="D569" s="2">
-        <v>9.764185147685912E-3</v>
+        <v>9.7999999999999997E-3</v>
       </c>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.2">
@@ -8563,13 +8686,13 @@
         <v>23</v>
       </c>
       <c r="B570" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C570" t="s">
         <v>32</v>
       </c>
       <c r="D570" s="2">
-        <v>9.9209288986234091E-3</v>
+        <v>9.9000000000000008E-3</v>
       </c>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.2">
@@ -8577,13 +8700,13 @@
         <v>24</v>
       </c>
       <c r="B571" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C571" t="s">
         <v>32</v>
       </c>
       <c r="D571" s="2">
-        <v>1.583616003658056E-2</v>
+        <v>1.5800000000000002E-2</v>
       </c>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.2">
@@ -8591,13 +8714,13 @@
         <v>25</v>
       </c>
       <c r="B572" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C572" t="s">
         <v>32</v>
       </c>
       <c r="D572" s="2">
-        <v>1.0440346002443507E-2</v>
+        <v>1.04E-2</v>
       </c>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.2">
@@ -8605,13 +8728,13 @@
         <v>26</v>
       </c>
       <c r="B573" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C573" t="s">
         <v>32</v>
       </c>
       <c r="D573" s="2">
-        <v>2.2132678428590354E-2</v>
+        <v>2.2100000000000002E-2</v>
       </c>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.2">
@@ -8619,13 +8742,13 @@
         <v>27</v>
       </c>
       <c r="B574" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C574" t="s">
         <v>32</v>
       </c>
       <c r="D574" s="2">
-        <v>9.9966083143998644E-3</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.2">
@@ -8633,13 +8756,13 @@
         <v>36</v>
       </c>
       <c r="B575" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C575" t="s">
         <v>32</v>
       </c>
       <c r="D575" s="2">
-        <v>9.6402068374821289E-3</v>
+        <v>9.5999999999999992E-3</v>
       </c>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.2">
@@ -8647,13 +8770,13 @@
         <v>28</v>
       </c>
       <c r="B576" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C576" t="s">
         <v>32</v>
       </c>
       <c r="D576" s="2">
-        <v>5.1755977700331229E-3</v>
+        <v>5.1999999999999998E-3</v>
       </c>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.2">
@@ -8661,13 +8784,13 @@
         <v>29</v>
       </c>
       <c r="B577" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C577" t="s">
         <v>32</v>
       </c>
       <c r="D577" s="2">
-        <v>1.611690239856834E-2</v>
+        <v>1.61E-2</v>
       </c>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.2">
@@ -8681,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="D578" s="2">
-        <v>0</v>
+        <v>1.5800000000000002E-2</v>
       </c>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.2">
@@ -8695,7 +8818,7 @@
         <v>0</v>
       </c>
       <c r="D579" s="2">
-        <v>0</v>
+        <v>5.6300000000000003E-2</v>
       </c>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.2">
@@ -8709,7 +8832,7 @@
         <v>0</v>
       </c>
       <c r="D580" s="2">
-        <v>0</v>
+        <v>7.51E-2</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.2">
@@ -8723,7 +8846,7 @@
         <v>0</v>
       </c>
       <c r="D581" s="2">
-        <v>0</v>
+        <v>2.87E-2</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.2">
@@ -8737,7 +8860,7 @@
         <v>0</v>
       </c>
       <c r="D582" s="2">
-        <v>0</v>
+        <v>2.5399999999999999E-2</v>
       </c>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.2">
@@ -8751,7 +8874,7 @@
         <v>0</v>
       </c>
       <c r="D583" s="2">
-        <v>0</v>
+        <v>3.6200000000000003E-2</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.2">
@@ -8765,7 +8888,7 @@
         <v>0</v>
       </c>
       <c r="D584" s="2">
-        <v>3.7187789084181587E-3</v>
+        <v>1.11E-2</v>
       </c>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.2">
@@ -8779,7 +8902,7 @@
         <v>0</v>
       </c>
       <c r="D585" s="2">
-        <v>1.8839628831193243E-3</v>
+        <v>3.0700000000000002E-2</v>
       </c>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.2">
@@ -8793,7 +8916,7 @@
         <v>0</v>
       </c>
       <c r="D586" s="2">
-        <v>0</v>
+        <v>5.9299999999999999E-2</v>
       </c>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.2">
@@ -8807,7 +8930,7 @@
         <v>0</v>
       </c>
       <c r="D587" s="2">
-        <v>0</v>
+        <v>1.95E-2</v>
       </c>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.2">
@@ -8821,7 +8944,7 @@
         <v>0</v>
       </c>
       <c r="D588" s="2">
-        <v>0</v>
+        <v>2.5499999999999998E-2</v>
       </c>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.2">
@@ -8835,7 +8958,7 @@
         <v>0</v>
       </c>
       <c r="D589" s="2">
-        <v>4.1927409261576969E-3</v>
+        <v>2.4799999999999999E-2</v>
       </c>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.2">
@@ -8849,7 +8972,7 @@
         <v>0</v>
       </c>
       <c r="D590" s="2">
-        <v>0</v>
+        <v>-4.41E-2</v>
       </c>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.2">
@@ -8863,7 +8986,7 @@
         <v>0</v>
       </c>
       <c r="D591" s="2">
-        <v>0</v>
+        <v>4.2099999999999999E-2</v>
       </c>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.2">
@@ -8877,7 +9000,7 @@
         <v>0</v>
       </c>
       <c r="D592" s="2">
-        <v>0</v>
+        <v>-3.4099999999999998E-2</v>
       </c>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.2">
@@ -8891,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="D593" s="2">
-        <v>0</v>
+        <v>1.9099999999999999E-2</v>
       </c>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.2">
@@ -8905,7 +9028,7 @@
         <v>0</v>
       </c>
       <c r="D594" s="2">
-        <v>0</v>
+        <v>1.2200000000000001E-2</v>
       </c>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.2">
@@ -8919,7 +9042,7 @@
         <v>0</v>
       </c>
       <c r="D595" s="2">
-        <v>0</v>
+        <v>9.2399999999999996E-2</v>
       </c>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.2">
@@ -8933,7 +9056,7 @@
         <v>0</v>
       </c>
       <c r="D596" s="2">
-        <v>0</v>
+        <v>1.3100000000000001E-2</v>
       </c>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.2">
@@ -8947,7 +9070,7 @@
         <v>0</v>
       </c>
       <c r="D597" s="2">
-        <v>0</v>
+        <v>3.5799999999999998E-2</v>
       </c>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.2">
@@ -8961,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="D598" s="2">
-        <v>1.3975803087192308E-3</v>
+        <v>1.89E-2</v>
       </c>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.2">
@@ -8975,7 +9098,7 @@
         <v>0</v>
       </c>
       <c r="D599" s="2">
-        <v>0</v>
+        <v>1.55E-2</v>
       </c>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.2">
@@ -8989,7 +9112,7 @@
         <v>0</v>
       </c>
       <c r="D600" s="2">
-        <v>3.2770848618244013E-3</v>
+        <v>2.3800000000000002E-2</v>
       </c>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.2">
@@ -9003,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="D601" s="2">
-        <v>0</v>
+        <v>8.3999999999999995E-3</v>
       </c>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.2">
@@ -9017,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="D602" s="2">
-        <v>0</v>
+        <v>1.41E-2</v>
       </c>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.2">
@@ -9031,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="D603" s="2">
-        <v>0</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.2">
@@ -9045,7 +9168,7 @@
         <v>0</v>
       </c>
       <c r="D604" s="2">
-        <v>0</v>
+        <v>1.61E-2</v>
       </c>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.2">
@@ -9073,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="D606" s="2">
-        <v>0</v>
+        <v>1.6500000000000001E-2</v>
       </c>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.2">
@@ -9087,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="D607" s="2">
-        <v>0.1</v>
+        <v>2.3800000000000002E-2</v>
       </c>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.2">
@@ -9101,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="D608" s="2">
-        <v>0</v>
+        <v>2.3E-2</v>
       </c>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.2">
@@ -9115,7 +9238,7 @@
         <v>0</v>
       </c>
       <c r="D609" s="2">
-        <v>0</v>
+        <v>-1.4E-2</v>
       </c>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.2">
@@ -9128,7 +9251,7 @@
       <c r="C610" t="s">
         <v>0</v>
       </c>
-      <c r="D610" s="2">
+      <c r="D610" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9142,7 +9265,7 @@
       <c r="C611" t="s">
         <v>0</v>
       </c>
-      <c r="D611" s="2">
+      <c r="D611" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9156,7 +9279,7 @@
       <c r="C612" t="s">
         <v>0</v>
       </c>
-      <c r="D612" s="2">
+      <c r="D612" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9170,7 +9293,7 @@
       <c r="C613" t="s">
         <v>0</v>
       </c>
-      <c r="D613" s="2">
+      <c r="D613" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9184,7 +9307,7 @@
       <c r="C614" t="s">
         <v>0</v>
       </c>
-      <c r="D614" s="2">
+      <c r="D614" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9198,7 +9321,7 @@
       <c r="C615" t="s">
         <v>0</v>
       </c>
-      <c r="D615" s="2">
+      <c r="D615" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9212,8 +9335,8 @@
       <c r="C616" t="s">
         <v>0</v>
       </c>
-      <c r="D616" s="2">
-        <v>1.5074557883597046E-3</v>
+      <c r="D616" s="6">
+        <v>1.5E-3</v>
       </c>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.2">
@@ -9226,8 +9349,8 @@
       <c r="C617" t="s">
         <v>0</v>
       </c>
-      <c r="D617" s="2">
-        <v>3.2207765969823328E-3</v>
+      <c r="D617" s="6">
+        <v>3.2000000000000002E-3</v>
       </c>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.2">
@@ -9240,7 +9363,7 @@
       <c r="C618" t="s">
         <v>0</v>
       </c>
-      <c r="D618" s="2">
+      <c r="D618" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9254,8 +9377,8 @@
       <c r="C619" t="s">
         <v>0</v>
       </c>
-      <c r="D619" s="2">
-        <v>2.6670802706464953E-3</v>
+      <c r="D619" s="6">
+        <v>2.7000000000000001E-3</v>
       </c>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.2">
@@ -9268,7 +9391,7 @@
       <c r="C620" t="s">
         <v>0</v>
       </c>
-      <c r="D620" s="2">
+      <c r="D620" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9282,7 +9405,7 @@
       <c r="C621" t="s">
         <v>0</v>
       </c>
-      <c r="D621" s="2">
+      <c r="D621" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9296,7 +9419,7 @@
       <c r="C622" t="s">
         <v>0</v>
       </c>
-      <c r="D622" s="2">
+      <c r="D622" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9310,7 +9433,7 @@
       <c r="C623" t="s">
         <v>0</v>
       </c>
-      <c r="D623" s="2">
+      <c r="D623" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9324,7 +9447,7 @@
       <c r="C624" t="s">
         <v>0</v>
       </c>
-      <c r="D624" s="2">
+      <c r="D624" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9338,7 +9461,7 @@
       <c r="C625" t="s">
         <v>0</v>
       </c>
-      <c r="D625" s="2">
+      <c r="D625" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9352,7 +9475,7 @@
       <c r="C626" t="s">
         <v>0</v>
       </c>
-      <c r="D626" s="2">
+      <c r="D626" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9366,7 +9489,7 @@
       <c r="C627" t="s">
         <v>0</v>
       </c>
-      <c r="D627" s="2">
+      <c r="D627" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9380,7 +9503,7 @@
       <c r="C628" t="s">
         <v>0</v>
       </c>
-      <c r="D628" s="2">
+      <c r="D628" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9394,7 +9517,7 @@
       <c r="C629" t="s">
         <v>0</v>
       </c>
-      <c r="D629" s="2">
+      <c r="D629" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9408,8 +9531,8 @@
       <c r="C630" t="s">
         <v>0</v>
       </c>
-      <c r="D630" s="2">
-        <v>2.5617586969778222E-3</v>
+      <c r="D630" s="6">
+        <v>2.5999999999999999E-3</v>
       </c>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.2">
@@ -9422,7 +9545,7 @@
       <c r="C631" t="s">
         <v>0</v>
       </c>
-      <c r="D631" s="2">
+      <c r="D631" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9436,7 +9559,7 @@
       <c r="C632" t="s">
         <v>0</v>
       </c>
-      <c r="D632" s="2">
+      <c r="D632" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9450,7 +9573,7 @@
       <c r="C633" t="s">
         <v>0</v>
       </c>
-      <c r="D633" s="2">
+      <c r="D633" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9464,7 +9587,7 @@
       <c r="C634" t="s">
         <v>0</v>
       </c>
-      <c r="D634" s="2">
+      <c r="D634" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9478,7 +9601,7 @@
       <c r="C635" t="s">
         <v>0</v>
       </c>
-      <c r="D635" s="2">
+      <c r="D635" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9492,7 +9615,7 @@
       <c r="C636" t="s">
         <v>0</v>
       </c>
-      <c r="D636" s="2">
+      <c r="D636" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9506,7 +9629,7 @@
       <c r="C637" t="s">
         <v>0</v>
       </c>
-      <c r="D637" s="2">
+      <c r="D637" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9520,7 +9643,7 @@
       <c r="C638" t="s">
         <v>0</v>
       </c>
-      <c r="D638" s="2">
+      <c r="D638" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9534,7 +9657,7 @@
       <c r="C639" t="s">
         <v>0</v>
       </c>
-      <c r="D639" s="2">
+      <c r="D639" s="6">
         <v>0.1</v>
       </c>
     </row>
@@ -9548,7 +9671,7 @@
       <c r="C640" t="s">
         <v>0</v>
       </c>
-      <c r="D640" s="2">
+      <c r="D640" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9562,7 +9685,7 @@
       <c r="C641" t="s">
         <v>0</v>
       </c>
-      <c r="D641" s="2">
+      <c r="D641" s="6">
         <v>0</v>
       </c>
     </row>
@@ -9571,13 +9694,13 @@
         <v>2</v>
       </c>
       <c r="B642" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C642" t="s">
         <v>1</v>
       </c>
-      <c r="D642" s="3">
-        <v>19</v>
+      <c r="D642" s="6">
+        <v>18</v>
       </c>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.2">
@@ -9585,13 +9708,13 @@
         <v>3</v>
       </c>
       <c r="B643" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C643" t="s">
         <v>1</v>
       </c>
-      <c r="D643" s="3">
-        <v>11</v>
+      <c r="D643" s="6">
+        <v>9</v>
       </c>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.2">
@@ -9599,13 +9722,13 @@
         <v>4</v>
       </c>
       <c r="B644" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C644" t="s">
         <v>1</v>
       </c>
-      <c r="D644" s="3">
-        <v>3</v>
+      <c r="D644" s="6">
+        <v>1</v>
       </c>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.2">
@@ -9613,13 +9736,13 @@
         <v>5</v>
       </c>
       <c r="B645" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C645" t="s">
         <v>1</v>
       </c>
-      <c r="D645" s="3">
-        <v>4</v>
+      <c r="D645" s="6">
+        <v>12</v>
       </c>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.2">
@@ -9627,12 +9750,12 @@
         <v>33</v>
       </c>
       <c r="B646" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C646" t="s">
         <v>1</v>
       </c>
-      <c r="D646" s="3">
+      <c r="D646" s="6">
         <v>7</v>
       </c>
     </row>
@@ -9641,13 +9764,13 @@
         <v>6</v>
       </c>
       <c r="B647" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C647" t="s">
         <v>1</v>
       </c>
-      <c r="D647" s="3">
-        <v>22</v>
+      <c r="D647" s="6">
+        <v>27</v>
       </c>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.2">
@@ -9655,13 +9778,13 @@
         <v>7</v>
       </c>
       <c r="B648" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C648" t="s">
         <v>1</v>
       </c>
-      <c r="D648" s="3">
-        <v>12</v>
+      <c r="D648" s="6">
+        <v>15</v>
       </c>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.2">
@@ -9669,12 +9792,12 @@
         <v>8</v>
       </c>
       <c r="B649" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C649" t="s">
         <v>1</v>
       </c>
-      <c r="D649" s="3">
+      <c r="D649" s="6">
         <v>2</v>
       </c>
     </row>
@@ -9683,13 +9806,13 @@
         <v>9</v>
       </c>
       <c r="B650" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C650" t="s">
         <v>1</v>
       </c>
-      <c r="D650" s="3">
-        <v>9</v>
+      <c r="D650" s="6">
+        <v>6</v>
       </c>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.2">
@@ -9697,13 +9820,13 @@
         <v>10</v>
       </c>
       <c r="B651" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C651" t="s">
         <v>1</v>
       </c>
-      <c r="D651" s="3">
-        <v>30</v>
+      <c r="D651" s="6">
+        <v>25</v>
       </c>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.2">
@@ -9711,13 +9834,13 @@
         <v>11</v>
       </c>
       <c r="B652" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C652" t="s">
         <v>1</v>
       </c>
-      <c r="D652" s="3">
-        <v>6</v>
+      <c r="D652" s="6">
+        <v>4</v>
       </c>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.2">
@@ -9725,12 +9848,12 @@
         <v>12</v>
       </c>
       <c r="B653" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C653" t="s">
         <v>1</v>
       </c>
-      <c r="D653" s="3">
+      <c r="D653" s="6">
         <v>32</v>
       </c>
     </row>
@@ -9739,13 +9862,13 @@
         <v>13</v>
       </c>
       <c r="B654" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C654" t="s">
         <v>1</v>
       </c>
-      <c r="D654" s="3">
-        <v>27</v>
+      <c r="D654" s="6">
+        <v>30</v>
       </c>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.2">
@@ -9753,12 +9876,12 @@
         <v>14</v>
       </c>
       <c r="B655" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C655" t="s">
         <v>1</v>
       </c>
-      <c r="D655" s="3">
+      <c r="D655" s="6">
         <v>28</v>
       </c>
     </row>
@@ -9767,13 +9890,13 @@
         <v>35</v>
       </c>
       <c r="B656" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C656" t="s">
         <v>1</v>
       </c>
-      <c r="D656" s="3">
-        <v>17</v>
+      <c r="D656" s="6">
+        <v>22</v>
       </c>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.2">
@@ -9781,13 +9904,13 @@
         <v>34</v>
       </c>
       <c r="B657" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C657" t="s">
         <v>1</v>
       </c>
-      <c r="D657" s="3">
-        <v>18</v>
+      <c r="D657" s="6">
+        <v>16</v>
       </c>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.2">
@@ -9795,13 +9918,13 @@
         <v>15</v>
       </c>
       <c r="B658" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C658" t="s">
         <v>1</v>
       </c>
-      <c r="D658" s="3">
-        <v>14</v>
+      <c r="D658" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.2">
@@ -9809,13 +9932,13 @@
         <v>16</v>
       </c>
       <c r="B659" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C659" t="s">
         <v>1</v>
       </c>
-      <c r="D659" s="3">
-        <v>10</v>
+      <c r="D659" s="6">
+        <v>5</v>
       </c>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.2">
@@ -9823,12 +9946,12 @@
         <v>17</v>
       </c>
       <c r="B660" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C660" t="s">
         <v>1</v>
       </c>
-      <c r="D660" s="3">
+      <c r="D660" s="6">
         <v>8</v>
       </c>
     </row>
@@ -9837,13 +9960,13 @@
         <v>18</v>
       </c>
       <c r="B661" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C661" t="s">
         <v>1</v>
       </c>
-      <c r="D661" s="3">
-        <v>21</v>
+      <c r="D661" s="6">
+        <v>17</v>
       </c>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.2">
@@ -9851,13 +9974,13 @@
         <v>19</v>
       </c>
       <c r="B662" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C662" t="s">
         <v>1</v>
       </c>
-      <c r="D662" s="3">
-        <v>16</v>
+      <c r="D662" s="6">
+        <v>14</v>
       </c>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.2">
@@ -9865,13 +9988,13 @@
         <v>20</v>
       </c>
       <c r="B663" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C663" t="s">
         <v>1</v>
       </c>
-      <c r="D663" s="3">
-        <v>1</v>
+      <c r="D663" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.2">
@@ -9879,13 +10002,13 @@
         <v>21</v>
       </c>
       <c r="B664" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C664" t="s">
         <v>1</v>
       </c>
-      <c r="D664" s="3">
-        <v>15</v>
+      <c r="D664" s="6">
+        <v>20</v>
       </c>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.2">
@@ -9893,13 +10016,13 @@
         <v>22</v>
       </c>
       <c r="B665" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C665" t="s">
         <v>1</v>
       </c>
-      <c r="D665" s="3">
-        <v>31</v>
+      <c r="D665" s="6">
+        <v>29</v>
       </c>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.2">
@@ -9907,12 +10030,12 @@
         <v>23</v>
       </c>
       <c r="B666" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C666" t="s">
         <v>1</v>
       </c>
-      <c r="D666" s="3">
+      <c r="D666" s="6">
         <v>26</v>
       </c>
     </row>
@@ -9921,13 +10044,13 @@
         <v>24</v>
       </c>
       <c r="B667" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C667" t="s">
         <v>1</v>
       </c>
-      <c r="D667" s="3">
-        <v>13</v>
+      <c r="D667" s="6">
+        <v>11</v>
       </c>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.2">
@@ -9935,13 +10058,13 @@
         <v>25</v>
       </c>
       <c r="B668" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C668" t="s">
         <v>1</v>
       </c>
-      <c r="D668" s="3">
-        <v>29</v>
+      <c r="D668" s="6">
+        <v>24</v>
       </c>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.2">
@@ -9949,13 +10072,13 @@
         <v>26</v>
       </c>
       <c r="B669" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C669" t="s">
         <v>1</v>
       </c>
-      <c r="D669" s="3">
-        <v>23</v>
+      <c r="D669" s="6">
+        <v>31</v>
       </c>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.2">
@@ -9963,13 +10086,13 @@
         <v>27</v>
       </c>
       <c r="B670" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C670" t="s">
         <v>1</v>
       </c>
-      <c r="D670" s="3">
-        <v>25</v>
+      <c r="D670" s="6">
+        <v>23</v>
       </c>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.2">
@@ -9977,13 +10100,13 @@
         <v>36</v>
       </c>
       <c r="B671" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C671" t="s">
         <v>1</v>
       </c>
-      <c r="D671" s="3">
-        <v>5</v>
+      <c r="D671" s="6">
+        <v>10</v>
       </c>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.2">
@@ -9991,13 +10114,13 @@
         <v>28</v>
       </c>
       <c r="B672" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C672" t="s">
         <v>1</v>
       </c>
-      <c r="D672" s="3">
-        <v>20</v>
+      <c r="D672" s="6">
+        <v>19</v>
       </c>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.2">
@@ -10005,16 +10128,465 @@
         <v>29</v>
       </c>
       <c r="B673" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C673" t="s">
         <v>1</v>
       </c>
-      <c r="D673" s="3">
+      <c r="D673" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A674" t="s">
+        <v>2</v>
+      </c>
+      <c r="B674" t="s">
+        <v>53</v>
+      </c>
+      <c r="C674" t="s">
+        <v>32</v>
+      </c>
+      <c r="D674" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A675" t="s">
+        <v>3</v>
+      </c>
+      <c r="B675" t="s">
+        <v>53</v>
+      </c>
+      <c r="C675" t="s">
+        <v>32</v>
+      </c>
+      <c r="D675" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A676" t="s">
+        <v>4</v>
+      </c>
+      <c r="B676" t="s">
+        <v>53</v>
+      </c>
+      <c r="C676" t="s">
+        <v>32</v>
+      </c>
+      <c r="D676" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A677" t="s">
+        <v>5</v>
+      </c>
+      <c r="B677" t="s">
+        <v>53</v>
+      </c>
+      <c r="C677" t="s">
+        <v>32</v>
+      </c>
+      <c r="D677" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A678" t="s">
+        <v>33</v>
+      </c>
+      <c r="B678" t="s">
+        <v>53</v>
+      </c>
+      <c r="C678" t="s">
+        <v>32</v>
+      </c>
+      <c r="D678" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A679" t="s">
+        <v>6</v>
+      </c>
+      <c r="B679" t="s">
+        <v>53</v>
+      </c>
+      <c r="C679" t="s">
+        <v>32</v>
+      </c>
+      <c r="D679" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A680" t="s">
+        <v>7</v>
+      </c>
+      <c r="B680" t="s">
+        <v>53</v>
+      </c>
+      <c r="C680" t="s">
+        <v>32</v>
+      </c>
+      <c r="D680" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A681" t="s">
+        <v>8</v>
+      </c>
+      <c r="B681" t="s">
+        <v>53</v>
+      </c>
+      <c r="C681" t="s">
+        <v>32</v>
+      </c>
+      <c r="D681" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A682" t="s">
+        <v>9</v>
+      </c>
+      <c r="B682" t="s">
+        <v>53</v>
+      </c>
+      <c r="C682" t="s">
+        <v>32</v>
+      </c>
+      <c r="D682" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A683" t="s">
+        <v>10</v>
+      </c>
+      <c r="B683" t="s">
+        <v>53</v>
+      </c>
+      <c r="C683" t="s">
+        <v>32</v>
+      </c>
+      <c r="D683" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A684" t="s">
+        <v>11</v>
+      </c>
+      <c r="B684" t="s">
+        <v>53</v>
+      </c>
+      <c r="C684" t="s">
+        <v>32</v>
+      </c>
+      <c r="D684" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A685" t="s">
+        <v>12</v>
+      </c>
+      <c r="B685" t="s">
+        <v>53</v>
+      </c>
+      <c r="C685" t="s">
+        <v>32</v>
+      </c>
+      <c r="D685" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A686" t="s">
+        <v>13</v>
+      </c>
+      <c r="B686" t="s">
+        <v>53</v>
+      </c>
+      <c r="C686" t="s">
+        <v>32</v>
+      </c>
+      <c r="D686" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A687" t="s">
+        <v>14</v>
+      </c>
+      <c r="B687" t="s">
+        <v>53</v>
+      </c>
+      <c r="C687" t="s">
+        <v>32</v>
+      </c>
+      <c r="D687" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A688" t="s">
+        <v>35</v>
+      </c>
+      <c r="B688" t="s">
+        <v>53</v>
+      </c>
+      <c r="C688" t="s">
+        <v>32</v>
+      </c>
+      <c r="D688" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A689" t="s">
+        <v>34</v>
+      </c>
+      <c r="B689" t="s">
+        <v>53</v>
+      </c>
+      <c r="C689" t="s">
+        <v>32</v>
+      </c>
+      <c r="D689" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A690" t="s">
+        <v>15</v>
+      </c>
+      <c r="B690" t="s">
+        <v>53</v>
+      </c>
+      <c r="C690" t="s">
+        <v>32</v>
+      </c>
+      <c r="D690" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A691" t="s">
+        <v>16</v>
+      </c>
+      <c r="B691" t="s">
+        <v>53</v>
+      </c>
+      <c r="C691" t="s">
+        <v>32</v>
+      </c>
+      <c r="D691" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A692" t="s">
+        <v>17</v>
+      </c>
+      <c r="B692" t="s">
+        <v>53</v>
+      </c>
+      <c r="C692" t="s">
+        <v>32</v>
+      </c>
+      <c r="D692" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A693" t="s">
+        <v>18</v>
+      </c>
+      <c r="B693" t="s">
+        <v>53</v>
+      </c>
+      <c r="C693" t="s">
+        <v>32</v>
+      </c>
+      <c r="D693" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A694" t="s">
+        <v>19</v>
+      </c>
+      <c r="B694" t="s">
+        <v>53</v>
+      </c>
+      <c r="C694" t="s">
+        <v>32</v>
+      </c>
+      <c r="D694" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A695" t="s">
+        <v>20</v>
+      </c>
+      <c r="B695" t="s">
+        <v>53</v>
+      </c>
+      <c r="C695" t="s">
+        <v>32</v>
+      </c>
+      <c r="D695" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A696" t="s">
+        <v>21</v>
+      </c>
+      <c r="B696" t="s">
+        <v>53</v>
+      </c>
+      <c r="C696" t="s">
+        <v>32</v>
+      </c>
+      <c r="D696" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A697" t="s">
+        <v>22</v>
+      </c>
+      <c r="B697" t="s">
+        <v>53</v>
+      </c>
+      <c r="C697" t="s">
+        <v>32</v>
+      </c>
+      <c r="D697" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A698" t="s">
+        <v>23</v>
+      </c>
+      <c r="B698" t="s">
+        <v>53</v>
+      </c>
+      <c r="C698" t="s">
+        <v>32</v>
+      </c>
+      <c r="D698" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A699" t="s">
         <v>24</v>
       </c>
+      <c r="B699" t="s">
+        <v>53</v>
+      </c>
+      <c r="C699" t="s">
+        <v>32</v>
+      </c>
+      <c r="D699" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A700" t="s">
+        <v>25</v>
+      </c>
+      <c r="B700" t="s">
+        <v>53</v>
+      </c>
+      <c r="C700" t="s">
+        <v>32</v>
+      </c>
+      <c r="D700" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A701" t="s">
+        <v>26</v>
+      </c>
+      <c r="B701" t="s">
+        <v>53</v>
+      </c>
+      <c r="C701" t="s">
+        <v>32</v>
+      </c>
+      <c r="D701" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A702" t="s">
+        <v>27</v>
+      </c>
+      <c r="B702" t="s">
+        <v>53</v>
+      </c>
+      <c r="C702" t="s">
+        <v>32</v>
+      </c>
+      <c r="D702" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A703" t="s">
+        <v>36</v>
+      </c>
+      <c r="B703" t="s">
+        <v>53</v>
+      </c>
+      <c r="C703" t="s">
+        <v>32</v>
+      </c>
+      <c r="D703" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A704" t="s">
+        <v>28</v>
+      </c>
+      <c r="B704" t="s">
+        <v>53</v>
+      </c>
+      <c r="C704" t="s">
+        <v>32</v>
+      </c>
+      <c r="D704" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A705" t="s">
+        <v>29</v>
+      </c>
+      <c r="B705" t="s">
+        <v>53</v>
+      </c>
+      <c r="C705" t="s">
+        <v>32</v>
+      </c>
+      <c r="D705" s="2">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D705" xr:uid="{6E624299-13BA-7F4D-9A79-35D067BBBF11}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>